--- a/database/event/4326/event_4326_evp_summary.xlsx
+++ b/database/event/4326/event_4326_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.4906</v>
+        <v>6.6872</v>
       </c>
       <c r="C2" t="n">
-        <v>1.837</v>
+        <v>2.2374</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7967</v>
+        <v>2.2203</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4906</v>
+        <v>6.6872</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1931</v>
+        <v>4.3897</v>
       </c>
       <c r="G2" t="n">
         <v>2.2975</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1931</v>
+        <v>4.58</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2229</v>
+        <v>4.6574</v>
       </c>
       <c r="J2" t="n">
         <v>2.2975</v>
@@ -529,7 +529,7 @@
         <v>71</v>
       </c>
       <c r="M2" t="n">
-        <v>5.5204</v>
+        <v>6.9549</v>
       </c>
       <c r="N2" t="n">
         <v>213</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.9708</v>
+        <v>4.3856</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3285</v>
+        <v>1.4673</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1828</v>
+        <v>1.3033</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9708</v>
+        <v>4.3856</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9566</v>
+        <v>3.3714</v>
       </c>
       <c r="G3" t="n">
         <v>1.0142</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9566</v>
+        <v>3.3714</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9842</v>
+        <v>3.4284</v>
       </c>
       <c r="J3" t="n">
         <v>1.0142</v>
@@ -575,7 +575,7 @@
         <v>71</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9984</v>
+        <v>4.4426</v>
       </c>
       <c r="N3" t="n">
         <v>213</v>
@@ -584,219 +584,219 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.711</v>
+        <v>3.2558</v>
       </c>
       <c r="C4" t="n">
-        <v>0.907</v>
+        <v>1.0893</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6738</v>
+        <v>0.8532</v>
       </c>
       <c r="E4" t="n">
-        <v>2.711</v>
+        <v>3.2558</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2234</v>
+        <v>4.1124</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4876</v>
+        <v>-0.8566</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2234</v>
+        <v>4.1452</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2255</v>
+        <v>4.1452</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4876</v>
+        <v>-0.8566</v>
       </c>
       <c r="K4" t="n">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="L4" t="n">
         <v>71</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7131</v>
+        <v>3.2886</v>
       </c>
       <c r="N4" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.5696</v>
+        <v>2.9864</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8597</v>
+        <v>0.9992</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6167</v>
+        <v>0.7459</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5696</v>
+        <v>2.9864</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5696</v>
+        <v>3.9864</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5696</v>
+        <v>3.9864</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5696</v>
+        <v>3.9864</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K5" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5696</v>
+        <v>2.9864</v>
       </c>
       <c r="N5" t="n">
-        <v>133</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.2977</v>
+        <v>2.8808</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7687</v>
+        <v>0.9638</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5069</v>
+        <v>0.7038</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2977</v>
+        <v>2.8808</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2476</v>
+        <v>2.8808</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0501</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2476</v>
+        <v>2.8808</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2476</v>
+        <v>2.8808</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0501</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="L6" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.2977</v>
+        <v>2.8808</v>
       </c>
       <c r="N6" t="n">
-        <v>191</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.9571</v>
+        <v>2.86</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6548</v>
+        <v>0.9569</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3693</v>
+        <v>0.6955</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9571</v>
+        <v>2.86</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8137</v>
+        <v>0.3724</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8566</v>
+        <v>2.4876</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8137</v>
+        <v>0.3724</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8137</v>
+        <v>0.3787</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8566</v>
+        <v>2.4876</v>
       </c>
       <c r="K7" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="L7" t="n">
         <v>71</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9571</v>
+        <v>2.8663</v>
       </c>
       <c r="N7" t="n">
-        <v>191</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.7186</v>
+        <v>2.59</v>
       </c>
       <c r="C8" t="n">
-        <v>0.575</v>
+        <v>0.8665</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2729</v>
+        <v>0.5879</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7186</v>
+        <v>2.59</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7186</v>
+        <v>2.5399</v>
       </c>
       <c r="G8" t="n">
-        <v>-1</v>
+        <v>0.0501</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7186</v>
+        <v>2.5399</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7186</v>
+        <v>2.5399</v>
       </c>
       <c r="J8" t="n">
-        <v>-1</v>
+        <v>0.0501</v>
       </c>
       <c r="K8" t="n">
         <v>120</v>
@@ -805,7 +805,7 @@
         <v>71</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7186</v>
+        <v>2.59</v>
       </c>
       <c r="N8" t="n">
         <v>191</v>
@@ -814,32 +814,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5227</v>
+        <v>1.96</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5095</v>
+        <v>0.6558</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1938</v>
+        <v>0.337</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5227</v>
+        <v>1.96</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5227</v>
+        <v>1.96</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5227</v>
+        <v>1.96</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5227</v>
+        <v>1.96</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5227</v>
+        <v>1.96</v>
       </c>
       <c r="N9" t="n">
         <v>133</v>
@@ -860,32 +860,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.4492</v>
+        <v>1.824</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4849</v>
+        <v>0.6103</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1641</v>
+        <v>0.2828</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4492</v>
+        <v>1.824</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4492</v>
+        <v>1.824</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4492</v>
+        <v>1.824</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4492</v>
+        <v>1.824</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4492</v>
+        <v>1.824</v>
       </c>
       <c r="N10" t="n">
         <v>133</v>
@@ -906,262 +906,262 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.322</v>
+        <v>1.7547</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4423</v>
+        <v>0.5871</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1127</v>
+        <v>0.2552</v>
       </c>
       <c r="E11" t="n">
-        <v>1.322</v>
+        <v>1.7547</v>
       </c>
       <c r="F11" t="n">
-        <v>0.654</v>
+        <v>2.0172</v>
       </c>
       <c r="G11" t="n">
-        <v>0.668</v>
+        <v>-0.2625</v>
       </c>
       <c r="H11" t="n">
-        <v>0.654</v>
+        <v>2.0172</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6601</v>
+        <v>2.0172</v>
       </c>
       <c r="J11" t="n">
-        <v>0.668</v>
+        <v>-0.2625</v>
       </c>
       <c r="K11" t="n">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="L11" t="n">
         <v>71</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3281</v>
+        <v>1.7547</v>
       </c>
       <c r="N11" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.1021</v>
+        <v>1.7377</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3687</v>
+        <v>0.5814</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0239</v>
+        <v>0.2484</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1021</v>
+        <v>1.7377</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3646</v>
+        <v>1.7377</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2625</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3646</v>
+        <v>1.7377</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3646</v>
+        <v>1.7377</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2625</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1021</v>
+        <v>1.7377</v>
       </c>
       <c r="N12" t="n">
-        <v>191</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.0016</v>
+        <v>1.5093</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3351</v>
+        <v>0.505</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0167</v>
+        <v>0.1574</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0016</v>
+        <v>1.5093</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0016</v>
+        <v>1.5548</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.0455</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0016</v>
+        <v>1.5548</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0016</v>
+        <v>1.5548</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.0455</v>
       </c>
       <c r="K13" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0016</v>
+        <v>1.5093</v>
       </c>
       <c r="N13" t="n">
-        <v>133</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9989</v>
+        <v>1.4151</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3342</v>
+        <v>0.4735</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0178</v>
+        <v>0.1199</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9989</v>
+        <v>1.4151</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9989</v>
+        <v>1.4151</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9989</v>
+        <v>1.4151</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9989</v>
+        <v>1.4151</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9989</v>
+        <v>1.4151</v>
       </c>
       <c r="N14" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6535</v>
+        <v>1.4138</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2186</v>
+        <v>0.473</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1574</v>
+        <v>0.1193</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6535</v>
+        <v>1.4138</v>
       </c>
       <c r="F15" t="n">
-        <v>0.699</v>
+        <v>0.7458</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0455</v>
+        <v>0.668</v>
       </c>
       <c r="H15" t="n">
-        <v>0.699</v>
+        <v>0.7458</v>
       </c>
       <c r="I15" t="n">
-        <v>0.699</v>
+        <v>0.7584</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0455</v>
+        <v>0.668</v>
       </c>
       <c r="K15" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="L15" t="n">
         <v>71</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6535</v>
+        <v>1.4264</v>
       </c>
       <c r="N15" t="n">
-        <v>191</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4588</v>
+        <v>1.1617</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1535</v>
+        <v>0.3887</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.236</v>
+        <v>0.0189</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4588</v>
+        <v>1.1617</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4588</v>
+        <v>1.1617</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4588</v>
+        <v>1.1617</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4588</v>
+        <v>1.1617</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4588</v>
+        <v>1.1617</v>
       </c>
       <c r="N16" t="n">
         <v>128</v>
@@ -1182,32 +1182,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3178</v>
+        <v>0.8318</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1063</v>
+        <v>0.2783</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.293</v>
+        <v>-0.1125</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3178</v>
+        <v>0.8318</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3178</v>
+        <v>0.8318</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3178</v>
+        <v>0.8318</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3178</v>
+        <v>0.8318</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3178</v>
+        <v>0.8318</v>
       </c>
       <c r="N17" t="n">
         <v>128</v>
@@ -1238,7 +1238,7 @@
         <v>-0.0291</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4565</v>
+        <v>-0.4786</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0871</v>
@@ -1284,7 +1284,7 @@
         <v>-0.0407</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4705</v>
+        <v>-0.4924</v>
       </c>
       <c r="E19" t="n">
         <v>-0.1216</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.2011</v>
+        <v>-0.1385</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0673</v>
+        <v>-0.0463</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5026</v>
+        <v>-0.4991</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2011</v>
+        <v>-0.1385</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2011</v>
+        <v>-0.1385</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2011</v>
+        <v>-0.1385</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2011</v>
+        <v>-0.1385</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2011</v>
+        <v>-0.1385</v>
       </c>
       <c r="N20" t="n">
         <v>122</v>
@@ -1376,7 +1376,7 @@
         <v>-0.0994</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5414</v>
+        <v>-0.5623</v>
       </c>
       <c r="E21" t="n">
         <v>-0.2972</v>
@@ -1422,7 +1422,7 @@
         <v>-0.1164</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5619</v>
+        <v>-0.5826</v>
       </c>
       <c r="E22" t="n">
         <v>-0.348</v>
@@ -1468,7 +1468,7 @@
         <v>-0.1703</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6269</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="E23" t="n">
         <v>-0.5089</v>
@@ -1514,7 +1514,7 @@
         <v>-0.2947</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7771</v>
+        <v>-0.7948</v>
       </c>
       <c r="E24" t="n">
         <v>-0.8807</v>
@@ -1560,7 +1560,7 @@
         <v>-0.2994</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.8004</v>
       </c>
       <c r="E25" t="n">
         <v>-0.8948</v>
@@ -1596,78 +1596,78 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.1129</v>
+        <v>-0.9494</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3723</v>
+        <v>-0.3176</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8709</v>
+        <v>-0.8222</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.1129</v>
+        <v>-0.9494</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1129</v>
+        <v>-1.186</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.2366</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.1129</v>
+        <v>-1.186</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.1129</v>
+        <v>-1.2061</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.2366</v>
       </c>
       <c r="K26" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.1129</v>
+        <v>-0.9694999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>125</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.1872</v>
+        <v>-1.1129</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3972</v>
+        <v>-0.3723</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.901</v>
+        <v>-0.8873</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.1872</v>
+        <v>-1.1129</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.1872</v>
+        <v>-1.1129</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.1872</v>
+        <v>-1.1129</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.1872</v>
+        <v>-1.1129</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.1872</v>
+        <v>-1.1129</v>
       </c>
       <c r="N27" t="n">
         <v>125</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.8202</v>
+        <v>-1.1872</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.609</v>
+        <v>-0.3972</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.1567</v>
+        <v>-0.9169</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.8202</v>
+        <v>-1.1872</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.0568</v>
+        <v>-1.1872</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2366</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.0568</v>
+        <v>-1.1872</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.076</v>
+        <v>-1.1872</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2366</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="L28" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.8394</v>
+        <v>-1.1872</v>
       </c>
       <c r="N28" t="n">
-        <v>213</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29">
@@ -1744,7 +1744,7 @@
         <v>-0.7181999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2885</v>
+        <v>-1.2991</v>
       </c>
       <c r="E29" t="n">
         <v>-2.1465</v>
@@ -1790,7 +1790,7 @@
         <v>-0.78</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.3632</v>
+        <v>-1.3727</v>
       </c>
       <c r="E30" t="n">
         <v>-2.3313</v>
@@ -1836,7 +1836,7 @@
         <v>-0.8922</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.4987</v>
+        <v>-1.5064</v>
       </c>
       <c r="E31" t="n">
         <v>-2.6668</v>

--- a/database/event/4326/event_4326_evp_summary.xlsx
+++ b/database/event/4326/event_4326_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6872</v>
+        <v>5.522</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2374</v>
+        <v>1.8475</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2203</v>
+        <v>1.8549</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6872</v>
+        <v>5.522</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3897</v>
+        <v>3.3907</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2975</v>
+        <v>2.1313</v>
       </c>
       <c r="H2" t="n">
-        <v>4.58</v>
+        <v>4.0855</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6574</v>
+        <v>4.4285</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2975</v>
+        <v>2.1313</v>
       </c>
       <c r="K2" t="n">
         <v>142</v>
@@ -529,7 +529,7 @@
         <v>71</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9549</v>
+        <v>6.559799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>213</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.3856</v>
+        <v>3.9979</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4673</v>
+        <v>1.3376</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3033</v>
+        <v>1.1668</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3856</v>
+        <v>3.9979</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3714</v>
+        <v>2.9869</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0142</v>
+        <v>1.011</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3714</v>
+        <v>3.1989</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4284</v>
+        <v>3.4674</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0142</v>
+        <v>1.011</v>
       </c>
       <c r="K3" t="n">
         <v>142</v>
@@ -575,7 +575,7 @@
         <v>71</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4426</v>
+        <v>4.4784</v>
       </c>
       <c r="N3" t="n">
         <v>213</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2558</v>
+        <v>3.0343</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0893</v>
+        <v>1.0152</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8532</v>
+        <v>0.7318</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2558</v>
+        <v>3.0343</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1124</v>
+        <v>2.8889</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8566</v>
+        <v>0.1454</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1452</v>
+        <v>2.9837</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1452</v>
+        <v>2.9837</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8566</v>
+        <v>0.1454</v>
       </c>
       <c r="K4" t="n">
         <v>120</v>
@@ -621,7 +621,7 @@
         <v>71</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2886</v>
+        <v>3.1291</v>
       </c>
       <c r="N4" t="n">
         <v>191</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.9864</v>
+        <v>2.9062</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9992</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7459</v>
+        <v>0.674</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9864</v>
+        <v>2.9062</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9864</v>
+        <v>3.458</v>
       </c>
       <c r="G5" t="n">
-        <v>-1</v>
+        <v>-0.5518</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9864</v>
+        <v>4.2334</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9864</v>
+        <v>4.2334</v>
       </c>
       <c r="J5" t="n">
-        <v>-1</v>
+        <v>-0.5518</v>
       </c>
       <c r="K5" t="n">
         <v>120</v>
@@ -667,7 +667,7 @@
         <v>71</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9864</v>
+        <v>3.6816</v>
       </c>
       <c r="N5" t="n">
         <v>191</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8808</v>
+        <v>2.8656</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9638</v>
+        <v>0.9587</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7038</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8808</v>
+        <v>2.8656</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8808</v>
+        <v>2.8656</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8808</v>
+        <v>2.9327</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8808</v>
+        <v>2.9327</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8808</v>
+        <v>2.9327</v>
       </c>
       <c r="N6" t="n">
         <v>133</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.86</v>
+        <v>2.7811</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9569</v>
+        <v>0.9305</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6955</v>
+        <v>0.6175</v>
       </c>
       <c r="E7" t="n">
-        <v>2.86</v>
+        <v>2.7811</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3724</v>
+        <v>0.5921</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4876</v>
+        <v>2.189</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3724</v>
+        <v>0.5921</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3787</v>
+        <v>0.6418</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4876</v>
+        <v>2.189</v>
       </c>
       <c r="K7" t="n">
         <v>142</v>
@@ -759,7 +759,7 @@
         <v>71</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8663</v>
+        <v>2.8308</v>
       </c>
       <c r="N7" t="n">
         <v>213</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.59</v>
+        <v>2.5494</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8665</v>
+        <v>0.853</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5879</v>
+        <v>0.5129</v>
       </c>
       <c r="E8" t="n">
-        <v>2.59</v>
+        <v>2.5494</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5399</v>
+        <v>3.3116</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0501</v>
+        <v>-0.7622</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5399</v>
+        <v>3.912</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5399</v>
+        <v>3.912</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0501</v>
+        <v>-0.7622</v>
       </c>
       <c r="K8" t="n">
         <v>120</v>
@@ -805,7 +805,7 @@
         <v>71</v>
       </c>
       <c r="M8" t="n">
-        <v>2.59</v>
+        <v>3.1498</v>
       </c>
       <c r="N8" t="n">
         <v>191</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.96</v>
+        <v>2.0931</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6558</v>
+        <v>0.7003</v>
       </c>
       <c r="D9" t="n">
-        <v>0.337</v>
+        <v>0.3069</v>
       </c>
       <c r="E9" t="n">
-        <v>1.96</v>
+        <v>2.0931</v>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>2.0931</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.96</v>
+        <v>2.0931</v>
       </c>
       <c r="I9" t="n">
-        <v>1.96</v>
+        <v>2.0931</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.96</v>
+        <v>2.0931</v>
       </c>
       <c r="N9" t="n">
         <v>133</v>
@@ -860,185 +860,185 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.824</v>
+        <v>2.0487</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6103</v>
+        <v>0.6854</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2828</v>
+        <v>0.2869</v>
       </c>
       <c r="E10" t="n">
-        <v>1.824</v>
+        <v>2.0487</v>
       </c>
       <c r="F10" t="n">
-        <v>1.824</v>
+        <v>2.2351</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.1864</v>
       </c>
       <c r="H10" t="n">
-        <v>1.824</v>
+        <v>2.2351</v>
       </c>
       <c r="I10" t="n">
-        <v>1.824</v>
+        <v>2.2351</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.1864</v>
       </c>
       <c r="K10" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M10" t="n">
-        <v>1.824</v>
+        <v>2.0487</v>
       </c>
       <c r="N10" t="n">
-        <v>133</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7547</v>
+        <v>1.9998</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5871</v>
+        <v>0.6691</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2552</v>
+        <v>0.2648</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7547</v>
+        <v>1.9998</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0172</v>
+        <v>1.9998</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2625</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0172</v>
+        <v>1.9998</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0172</v>
+        <v>1.9998</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2625</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="L11" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7547</v>
+        <v>1.9998</v>
       </c>
       <c r="N11" t="n">
-        <v>191</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7377</v>
+        <v>1.7602</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5814</v>
+        <v>0.5889</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2484</v>
+        <v>0.1566</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7377</v>
+        <v>1.7602</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7377</v>
+        <v>0.8621</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.8981</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7377</v>
+        <v>0.8621</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7377</v>
+        <v>0.9345</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.8981</v>
       </c>
       <c r="K12" t="n">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7377</v>
+        <v>1.8326</v>
       </c>
       <c r="N12" t="n">
-        <v>122</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5093</v>
+        <v>1.7185</v>
       </c>
       <c r="C13" t="n">
-        <v>0.505</v>
+        <v>0.575</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1574</v>
+        <v>0.1378</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5093</v>
+        <v>1.7185</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5548</v>
+        <v>1.7185</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0455</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5548</v>
+        <v>1.7185</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5548</v>
+        <v>1.7185</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0455</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L13" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5093</v>
+        <v>1.7185</v>
       </c>
       <c r="N13" t="n">
-        <v>191</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4151</v>
+        <v>1.5892</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4735</v>
+        <v>0.5317</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1199</v>
+        <v>0.0794</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4151</v>
+        <v>1.5892</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4151</v>
+        <v>1.5892</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4151</v>
+        <v>1.5892</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4151</v>
+        <v>1.5892</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4151</v>
+        <v>1.5892</v>
       </c>
       <c r="N14" t="n">
         <v>133</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4138</v>
+        <v>1.5791</v>
       </c>
       <c r="C15" t="n">
-        <v>0.473</v>
+        <v>0.5283</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1193</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4138</v>
+        <v>1.5791</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7458</v>
+        <v>1.6157</v>
       </c>
       <c r="G15" t="n">
-        <v>0.668</v>
+        <v>-0.0366</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7458</v>
+        <v>1.6157</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7584</v>
+        <v>1.6157</v>
       </c>
       <c r="J15" t="n">
-        <v>0.668</v>
+        <v>-0.0366</v>
       </c>
       <c r="K15" t="n">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="L15" t="n">
         <v>71</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4264</v>
+        <v>1.5791</v>
       </c>
       <c r="N15" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1617</v>
+        <v>1.0871</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3887</v>
+        <v>0.3637</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0189</v>
+        <v>-0.1472</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1617</v>
+        <v>1.0871</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1617</v>
+        <v>1.0871</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1617</v>
+        <v>1.0871</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1617</v>
+        <v>1.0871</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1617</v>
+        <v>1.0871</v>
       </c>
       <c r="N16" t="n">
         <v>128</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8318</v>
+        <v>0.9105</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2783</v>
+        <v>0.3046</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1125</v>
+        <v>-0.227</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8318</v>
+        <v>0.9105</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8318</v>
+        <v>0.9105</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8318</v>
+        <v>0.9105</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8318</v>
+        <v>0.9105</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8318</v>
+        <v>0.9105</v>
       </c>
       <c r="N17" t="n">
         <v>128</v>
@@ -1228,32 +1228,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0871</v>
+        <v>0.5003</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0291</v>
+        <v>0.1674</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4786</v>
+        <v>-0.4122</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0871</v>
+        <v>0.5003</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0871</v>
+        <v>0.5003</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0871</v>
+        <v>0.5003</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0871</v>
+        <v>0.5003</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0871</v>
+        <v>0.5003</v>
       </c>
       <c r="N18" t="n">
         <v>122</v>
@@ -1274,32 +1274,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.1216</v>
+        <v>0.3286</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0407</v>
+        <v>0.1099</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4924</v>
+        <v>-0.4897</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1216</v>
+        <v>0.3286</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1216</v>
+        <v>0.3286</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1216</v>
+        <v>0.3286</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1216</v>
+        <v>0.3286</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1216</v>
+        <v>0.3286</v>
       </c>
       <c r="N19" t="n">
         <v>122</v>
@@ -1320,32 +1320,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1385</v>
+        <v>0.319</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0463</v>
+        <v>0.1067</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4991</v>
+        <v>-0.494</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1385</v>
+        <v>0.319</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1385</v>
+        <v>0.319</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1385</v>
+        <v>0.319</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1385</v>
+        <v>0.319</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1385</v>
+        <v>0.319</v>
       </c>
       <c r="N20" t="n">
         <v>122</v>
@@ -1366,32 +1366,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2972</v>
+        <v>0.2611</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0994</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5623</v>
+        <v>-0.5201</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2972</v>
+        <v>0.2611</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2972</v>
+        <v>0.2611</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2972</v>
+        <v>0.2611</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2972</v>
+        <v>0.2611</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2972</v>
+        <v>0.2611</v>
       </c>
       <c r="N21" t="n">
         <v>122</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.348</v>
+        <v>-0.1005</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1164</v>
+        <v>-0.0336</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5826</v>
+        <v>-0.6834</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.348</v>
+        <v>-0.1005</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.348</v>
+        <v>-0.1005</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.348</v>
+        <v>-0.1005</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.348</v>
+        <v>-0.1005</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.348</v>
+        <v>-0.1005</v>
       </c>
       <c r="N22" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5089</v>
+        <v>-0.157</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1703</v>
+        <v>-0.0525</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.7089</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5089</v>
+        <v>-0.157</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5089</v>
+        <v>-0.157</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5089</v>
+        <v>-0.157</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5089</v>
+        <v>-0.157</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5089</v>
+        <v>-0.157</v>
       </c>
       <c r="N23" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.8807</v>
+        <v>-0.3131</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.2947</v>
+        <v>-0.1048</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7948</v>
+        <v>-0.7794</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8807</v>
+        <v>-0.3131</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8807</v>
+        <v>-0.3131</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8807</v>
+        <v>-0.3131</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8807</v>
+        <v>-0.3131</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8807</v>
+        <v>-0.3131</v>
       </c>
       <c r="N24" t="n">
         <v>125</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.8948</v>
+        <v>-0.4509</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.2994</v>
+        <v>-0.1509</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8004</v>
+        <v>-0.8416</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8948</v>
+        <v>-0.4509</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8948</v>
+        <v>-0.4509</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8948</v>
+        <v>-0.4509</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8948</v>
+        <v>-0.4509</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8948</v>
+        <v>-0.4509</v>
       </c>
       <c r="N25" t="n">
         <v>128</v>
@@ -1596,78 +1596,78 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.9494</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3176</v>
+        <v>-0.19</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8222</v>
+        <v>-0.8944</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9494</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.186</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2366</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.186</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.2061</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2366</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="L26" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.9694999999999999</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>213</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.1129</v>
+        <v>-0.7774</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3723</v>
+        <v>-0.2601</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8873</v>
+        <v>-0.989</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.1129</v>
+        <v>-0.7774</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.1129</v>
+        <v>-0.7774</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.1129</v>
+        <v>-0.7774</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.1129</v>
+        <v>-0.7774</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.1129</v>
+        <v>-0.7774</v>
       </c>
       <c r="N27" t="n">
         <v>125</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.1872</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3972</v>
+        <v>-0.3041</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9169</v>
+        <v>-1.0483</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.1872</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.1872</v>
+        <v>-1.1691</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.2603</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.1872</v>
+        <v>-1.1691</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.1872</v>
+        <v>-1.2672</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.2603</v>
       </c>
       <c r="K28" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.1872</v>
+        <v>-1.0069</v>
       </c>
       <c r="N28" t="n">
-        <v>125</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.1465</v>
+        <v>-1.4154</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.4736</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2991</v>
+        <v>-1.277</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.1465</v>
+        <v>-1.4154</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.1465</v>
+        <v>-1.4154</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.1465</v>
+        <v>-1.4154</v>
       </c>
       <c r="I29" t="n">
-        <v>-2.1465</v>
+        <v>-1.4154</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-2.1465</v>
+        <v>-1.4154</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.3313</v>
+        <v>-1.7575</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.78</v>
+        <v>-0.588</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.3727</v>
+        <v>-1.4314</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.3313</v>
+        <v>-1.7575</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.3313</v>
+        <v>-1.7575</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.3313</v>
+        <v>-1.7575</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.3313</v>
+        <v>-1.7575</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.3313</v>
+        <v>-1.7575</v>
       </c>
       <c r="N30" t="n">
         <v>128</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.6668</v>
+        <v>-2.0745</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.8922</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.5064</v>
+        <v>-1.5745</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.6668</v>
+        <v>-2.0745</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.6668</v>
+        <v>-2.0745</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.6668</v>
+        <v>-2.0745</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.6668</v>
+        <v>-2.0745</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.6668</v>
+        <v>-2.0745</v>
       </c>
       <c r="N31" t="n">
         <v>128</v>
@@ -1969,10 +1969,10 @@
         <v>1.24</v>
       </c>
       <c r="I2" t="n">
-        <v>0.451</v>
+        <v>0.4001</v>
       </c>
       <c r="J2" t="n">
-        <v>13.079</v>
+        <v>11.6029</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>0.223</v>
+        <v>0.1792</v>
       </c>
       <c r="J3" t="n">
-        <v>6.467</v>
+        <v>5.1968</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0417</v>
+        <v>-0.0339</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2093</v>
+        <v>-0.9831</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2512</v>
+        <v>-0.1525</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.2848</v>
+        <v>-4.4225</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.65</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5788</v>
+        <v>-0.3796</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.7852</v>
+        <v>-11.0084</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.21</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3647</v>
+        <v>0.3065</v>
       </c>
       <c r="J7" t="n">
-        <v>10.5763</v>
+        <v>8.888500000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.32</v>
+        <v>0.2684</v>
       </c>
       <c r="J8" t="n">
-        <v>9.279999999999999</v>
+        <v>7.7836</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2394</v>
+        <v>0.2031</v>
       </c>
       <c r="J9" t="n">
-        <v>6.9426</v>
+        <v>5.8899</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1386</v>
+        <v>0.1349</v>
       </c>
       <c r="J10" t="n">
-        <v>4.0194</v>
+        <v>3.9121</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2853</v>
+        <v>-0.1667</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.2737</v>
+        <v>-4.8343</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3243</v>
+        <v>1.205</v>
       </c>
       <c r="J12" t="n">
-        <v>31.7832</v>
+        <v>28.92</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3219</v>
+        <v>0.3677</v>
       </c>
       <c r="J13" t="n">
-        <v>7.7256</v>
+        <v>8.8248</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3219</v>
+        <v>0.3677</v>
       </c>
       <c r="J14" t="n">
-        <v>7.7256</v>
+        <v>8.8248</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.03</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0347</v>
+        <v>0.096</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8328</v>
+        <v>2.304</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.96</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2791</v>
+        <v>-0.2052</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.6984</v>
+        <v>-4.9248</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2084</v>
+        <v>0.2073</v>
       </c>
       <c r="J17" t="n">
-        <v>5.0016</v>
+        <v>4.9752</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>0.95</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0805</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.932</v>
+        <v>-1.6464</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1014</v>
+        <v>-0.0808</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.4336</v>
+        <v>-1.9392</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.144</v>
+        <v>-0.1038</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.456</v>
+        <v>-2.4912</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.516</v>
+        <v>-0.3355</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.384</v>
+        <v>-8.052</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.99</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9427</v>
+        <v>1.6421</v>
       </c>
       <c r="J22" t="n">
-        <v>34.9686</v>
+        <v>29.5578</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.74</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5246</v>
+        <v>1.3635</v>
       </c>
       <c r="J23" t="n">
-        <v>27.4428</v>
+        <v>24.543</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.64</v>
       </c>
       <c r="I24" t="n">
-        <v>1.335</v>
+        <v>1.2501</v>
       </c>
       <c r="J24" t="n">
-        <v>24.03</v>
+        <v>22.5018</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.58</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2121</v>
+        <v>1.1817</v>
       </c>
       <c r="J25" t="n">
-        <v>21.8178</v>
+        <v>21.2706</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.78</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8365</v>
+        <v>-0.7922</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.057</v>
+        <v>-14.2596</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.76</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2641</v>
+        <v>-0.2242</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.7538</v>
+        <v>-4.0356</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.7</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3579</v>
+        <v>-0.2857</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.4422</v>
+        <v>-5.1426</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.63</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4792</v>
+        <v>-0.3512</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.6256</v>
+        <v>-6.3216</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.61</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.523</v>
+        <v>-0.3684</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.414</v>
+        <v>-6.6312</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.44</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7702</v>
+        <v>-0.5269</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.8636</v>
+        <v>-9.4842</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2097</v>
+        <v>0.2254</v>
       </c>
       <c r="J32" t="n">
-        <v>6.291</v>
+        <v>6.762</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1544</v>
+        <v>0.1613</v>
       </c>
       <c r="J33" t="n">
-        <v>4.632</v>
+        <v>4.839</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0029</v>
+        <v>-0.0001</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.96</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1154</v>
+        <v>-0.0634</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.462</v>
+        <v>-1.902</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.9</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2285</v>
+        <v>-0.1345</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.855</v>
+        <v>-4.035</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.28</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4512</v>
+        <v>0.5427</v>
       </c>
       <c r="J37" t="n">
-        <v>13.536</v>
+        <v>16.281</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3376</v>
+        <v>0.4057</v>
       </c>
       <c r="J38" t="n">
-        <v>10.128</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.16</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2745</v>
+        <v>0.3349</v>
       </c>
       <c r="J39" t="n">
-        <v>8.234999999999999</v>
+        <v>10.047</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.06</v>
       </c>
       <c r="I40" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="J40" t="n">
-        <v>2.595</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.95</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1742</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.226</v>
+        <v>-2.682</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9053</v>
+        <v>0.9067</v>
       </c>
       <c r="J42" t="n">
-        <v>26.2537</v>
+        <v>26.2943</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.31</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8142</v>
+        <v>0.8159</v>
       </c>
       <c r="J43" t="n">
-        <v>23.6118</v>
+        <v>23.6611</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.25</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6684</v>
+        <v>0.677</v>
       </c>
       <c r="J44" t="n">
-        <v>19.3836</v>
+        <v>19.633</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.07</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1459</v>
+        <v>0.2144</v>
       </c>
       <c r="J45" t="n">
-        <v>4.2311</v>
+        <v>6.2176</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0141</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>0.4089</v>
+        <v>2.436</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.2</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4114</v>
+        <v>0.4673</v>
       </c>
       <c r="J47" t="n">
-        <v>11.9306</v>
+        <v>13.5517</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1477</v>
+        <v>0.135</v>
       </c>
       <c r="J48" t="n">
-        <v>4.2833</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3007</v>
+        <v>-0.1891</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.7203</v>
+        <v>-5.4839</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.78</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3925</v>
+        <v>-0.2495</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.3825</v>
+        <v>-7.2355</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.75</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4356</v>
+        <v>-0.2789</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.6324</v>
+        <v>-8.088100000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.2</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3808</v>
+        <v>0.4362</v>
       </c>
       <c r="J52" t="n">
-        <v>11.0432</v>
+        <v>12.6498</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2248</v>
+        <v>0.2444</v>
       </c>
       <c r="J53" t="n">
-        <v>6.5192</v>
+        <v>7.0876</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1894</v>
+        <v>0.2031</v>
       </c>
       <c r="J54" t="n">
-        <v>5.4926</v>
+        <v>5.8899</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.91</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2131</v>
+        <v>-0.1239</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.1799</v>
+        <v>-3.5931</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4553</v>
+        <v>-0.2892</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.2037</v>
+        <v>-8.386799999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.33</v>
       </c>
       <c r="I57" t="n">
-        <v>0.892</v>
+        <v>0.8809</v>
       </c>
       <c r="J57" t="n">
-        <v>25.868</v>
+        <v>25.5461</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.18</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5235</v>
+        <v>0.5214</v>
       </c>
       <c r="J58" t="n">
-        <v>15.1815</v>
+        <v>15.1206</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.15</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4336</v>
+        <v>0.4464</v>
       </c>
       <c r="J59" t="n">
-        <v>12.5744</v>
+        <v>12.9456</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1332</v>
       </c>
       <c r="J60" t="n">
-        <v>2.1837</v>
+        <v>3.8628</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>1.02</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0011</v>
+        <v>0.0615</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0319</v>
+        <v>1.7835</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.88</v>
       </c>
       <c r="I62" t="n">
-        <v>1.9135</v>
+        <v>1.6141</v>
       </c>
       <c r="J62" t="n">
-        <v>53.578</v>
+        <v>45.1948</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7478</v>
+        <v>0.7489</v>
       </c>
       <c r="J63" t="n">
-        <v>20.9384</v>
+        <v>20.9692</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.03</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0173</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>0.4844</v>
+        <v>2.408</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.95</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3265</v>
+        <v>-0.2489</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.141999999999999</v>
+        <v>-6.9692</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.83</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6561</v>
+        <v>-0.5952</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.3708</v>
+        <v>-16.6656</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.28</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5392</v>
+        <v>0.6394</v>
       </c>
       <c r="J67" t="n">
-        <v>15.0976</v>
+        <v>17.9032</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.06</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2058</v>
+        <v>0.1986</v>
       </c>
       <c r="J68" t="n">
-        <v>5.7624</v>
+        <v>5.5608</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.83</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2976</v>
+        <v>-0.1937</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.332800000000001</v>
+        <v>-5.4236</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.63</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.586</v>
+        <v>-0.3868</v>
       </c>
       <c r="J70" t="n">
-        <v>-16.408</v>
+        <v>-10.8304</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.57</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6621</v>
+        <v>-0.4425</v>
       </c>
       <c r="J71" t="n">
-        <v>-18.5388</v>
+        <v>-12.39</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.58</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3475</v>
+        <v>1.2264</v>
       </c>
       <c r="J72" t="n">
-        <v>33.6875</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8448</v>
       </c>
       <c r="J73" t="n">
-        <v>20.5775</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.23</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5513</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>13.7825</v>
+        <v>15.5125</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.12</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2627</v>
+        <v>0.3426</v>
       </c>
       <c r="J75" t="n">
-        <v>6.5675</v>
+        <v>8.565</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.07</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1203</v>
+        <v>0.199</v>
       </c>
       <c r="J76" t="n">
-        <v>3.0075</v>
+        <v>4.975</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1379</v>
+        <v>0.1064</v>
       </c>
       <c r="J77" t="n">
-        <v>3.4475</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.89</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1294</v>
+        <v>-0.1189</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.235</v>
+        <v>-2.9725</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2491</v>
+        <v>-0.1939</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.2275</v>
+        <v>-4.8475</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.62</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5755</v>
+        <v>-0.3831</v>
       </c>
       <c r="J80" t="n">
-        <v>-14.3875</v>
+        <v>-9.577500000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6548</v>
+        <v>-0.4391</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.37</v>
+        <v>-10.9775</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>0.7</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.2998</v>
+        <v>-0.2561</v>
       </c>
       <c r="J82" t="n">
-        <v>-5.3964</v>
+        <v>-4.6098</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>0.55</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.5383</v>
+        <v>-0.4078</v>
       </c>
       <c r="J83" t="n">
-        <v>-9.689399999999999</v>
+        <v>-7.3404</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.54</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.5577</v>
+        <v>-0.4167</v>
       </c>
       <c r="J84" t="n">
-        <v>-10.0386</v>
+        <v>-7.5006</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.44</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.735</v>
+        <v>-0.5078</v>
       </c>
       <c r="J85" t="n">
-        <v>-13.23</v>
+        <v>-9.1404</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.43</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7496</v>
+        <v>-0.5174</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.4928</v>
+        <v>-9.3132</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.74</v>
       </c>
       <c r="I87" t="n">
-        <v>1.4999</v>
+        <v>1.3559</v>
       </c>
       <c r="J87" t="n">
-        <v>26.9982</v>
+        <v>24.4062</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.65</v>
       </c>
       <c r="I88" t="n">
-        <v>1.3252</v>
+        <v>1.2555</v>
       </c>
       <c r="J88" t="n">
-        <v>23.8536</v>
+        <v>22.599</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.61</v>
       </c>
       <c r="I89" t="n">
-        <v>1.2376</v>
+        <v>1.2112</v>
       </c>
       <c r="J89" t="n">
-        <v>22.2768</v>
+        <v>21.8016</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>1.58</v>
       </c>
       <c r="I90" t="n">
-        <v>1.1616</v>
+        <v>1.1781</v>
       </c>
       <c r="J90" t="n">
-        <v>20.9088</v>
+        <v>21.2058</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>1.44</v>
       </c>
       <c r="I91" t="n">
-        <v>0.8725000000000001</v>
+        <v>1.0062</v>
       </c>
       <c r="J91" t="n">
-        <v>15.705</v>
+        <v>18.1116</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.84</v>
       </c>
       <c r="I92" t="n">
-        <v>1.8157</v>
+        <v>1.5377</v>
       </c>
       <c r="J92" t="n">
-        <v>47.2082</v>
+        <v>39.9802</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.33</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8156</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="J93" t="n">
-        <v>21.2056</v>
+        <v>21.8972</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.22</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5181</v>
+        <v>0.5946</v>
       </c>
       <c r="J94" t="n">
-        <v>13.4706</v>
+        <v>15.4596</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0856</v>
+        <v>0.1653</v>
       </c>
       <c r="J95" t="n">
-        <v>2.2256</v>
+        <v>4.2978</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3829</v>
+        <v>-0.3016</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.955399999999999</v>
+        <v>-7.8416</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2635</v>
+        <v>0.2674</v>
       </c>
       <c r="J97" t="n">
-        <v>6.851</v>
+        <v>6.9524</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>0.86</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2016</v>
+        <v>-0.1583</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.2416</v>
+        <v>-4.1158</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>0.78</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3548</v>
+        <v>-0.2366</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.2248</v>
+        <v>-6.1516</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.72</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4476</v>
+        <v>-0.2943</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.6376</v>
+        <v>-7.6518</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.66</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5326</v>
+        <v>-0.3513</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.8476</v>
+        <v>-9.133800000000001</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.54</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2725</v>
+        <v>1.1781</v>
       </c>
       <c r="J102" t="n">
-        <v>30.54</v>
+        <v>28.2744</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7544</v>
+        <v>0.7792</v>
       </c>
       <c r="J103" t="n">
-        <v>18.1056</v>
+        <v>18.7008</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.23</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5555</v>
+        <v>0.6216</v>
       </c>
       <c r="J104" t="n">
-        <v>13.332</v>
+        <v>14.9184</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.14</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3193</v>
+        <v>0.3977</v>
       </c>
       <c r="J105" t="n">
-        <v>7.6632</v>
+        <v>9.5448</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>1.09</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1812</v>
+        <v>0.2597</v>
       </c>
       <c r="J106" t="n">
-        <v>4.3488</v>
+        <v>6.2328</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.03</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1706</v>
+        <v>0.1489</v>
       </c>
       <c r="J107" t="n">
-        <v>4.0944</v>
+        <v>3.5736</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>0.88</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1632</v>
+        <v>-0.136</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.9168</v>
+        <v>-3.264</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2524</v>
+        <v>-0.1881</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.0576</v>
+        <v>-4.5144</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.7</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4746</v>
+        <v>-0.3125</v>
       </c>
       <c r="J110" t="n">
-        <v>-11.3904</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.63</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5715</v>
+        <v>-0.3786</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.716</v>
+        <v>-9.086399999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2387</v>
+        <v>1.1557</v>
       </c>
       <c r="J112" t="n">
-        <v>28.4901</v>
+        <v>26.5811</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.4</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9906</v>
+        <v>0.9932</v>
       </c>
       <c r="J113" t="n">
-        <v>22.7838</v>
+        <v>22.8436</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.9026</v>
+        <v>0.9153</v>
       </c>
       <c r="J114" t="n">
-        <v>20.7598</v>
+        <v>21.0519</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2977</v>
+        <v>0.3738</v>
       </c>
       <c r="J115" t="n">
-        <v>6.8471</v>
+        <v>8.5974</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.83</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6694</v>
+        <v>-0.608</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.3962</v>
+        <v>-13.984</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.24</v>
       </c>
       <c r="I117" t="n">
-        <v>0.474</v>
+        <v>0.5502</v>
       </c>
       <c r="J117" t="n">
-        <v>10.902</v>
+        <v>12.6546</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1749</v>
+        <v>0.1646</v>
       </c>
       <c r="J118" t="n">
-        <v>4.0227</v>
+        <v>3.7858</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.92</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1368</v>
+        <v>-0.103</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.1464</v>
+        <v>-2.369</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.76</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4164</v>
+        <v>-0.2668</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.577199999999999</v>
+        <v>-6.1364</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6918</v>
+        <v>-0.4644</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.9114</v>
+        <v>-10.6812</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2628</v>
+        <v>1.1633</v>
       </c>
       <c r="J122" t="n">
-        <v>37.884</v>
+        <v>34.899</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.32</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8666</v>
       </c>
       <c r="J123" t="n">
-        <v>26.478</v>
+        <v>25.998</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.23</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6702</v>
+        <v>0.6511</v>
       </c>
       <c r="J124" t="n">
-        <v>20.106</v>
+        <v>19.533</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4214</v>
+        <v>-0.3534</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.642</v>
+        <v>-10.602</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.64</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.0668</v>
+        <v>-1.0504</v>
       </c>
       <c r="J126" t="n">
-        <v>-32.004</v>
+        <v>-31.512</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.274</v>
+        <v>0.2962</v>
       </c>
       <c r="J127" t="n">
-        <v>8.220000000000001</v>
+        <v>8.885999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0232</v>
+        <v>0.005</v>
       </c>
       <c r="J128" t="n">
-        <v>0.696</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.99</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0131</v>
+        <v>-0.0182</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.393</v>
+        <v>-0.546</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.91</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1982</v>
+        <v>-0.1194</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.946</v>
+        <v>-3.582</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3605</v>
+        <v>-0.2249</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.815</v>
+        <v>-6.747</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.76</v>
       </c>
       <c r="I132" t="n">
-        <v>1.7419</v>
+        <v>1.4878</v>
       </c>
       <c r="J132" t="n">
-        <v>47.0313</v>
+        <v>40.1706</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.47</v>
       </c>
       <c r="I133" t="n">
-        <v>1.192</v>
+        <v>1.1182</v>
       </c>
       <c r="J133" t="n">
-        <v>32.184</v>
+        <v>30.1914</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.97</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2384</v>
+        <v>-0.1665</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.4368</v>
+        <v>-4.4955</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.7143</v>
+        <v>-0.6603</v>
       </c>
       <c r="J135" t="n">
-        <v>-19.2861</v>
+        <v>-17.8281</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.7</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.9426</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>-25.4502</v>
+        <v>-24.5916</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4322</v>
+        <v>0.494</v>
       </c>
       <c r="J137" t="n">
-        <v>11.6694</v>
+        <v>13.338</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.096</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.592</v>
+        <v>-2.1519</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.9</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.184</v>
+        <v>-0.1245</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.968</v>
+        <v>-3.3615</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.76</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4164</v>
+        <v>-0.2668</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.2428</v>
+        <v>-7.2036</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4866</v>
+        <v>-0.3151</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.1382</v>
+        <v>-8.5077</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.1579</v>
+        <v>-0.1513</v>
       </c>
       <c r="J142" t="n">
-        <v>-3.0001</v>
+        <v>-2.8747</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>0.64</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.4217</v>
+        <v>-0.3329</v>
       </c>
       <c r="J143" t="n">
-        <v>-8.0123</v>
+        <v>-6.3251</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.6</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4883</v>
+        <v>-0.3708</v>
       </c>
       <c r="J144" t="n">
-        <v>-9.277699999999999</v>
+        <v>-7.0452</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.44</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.754</v>
+        <v>-0.5175</v>
       </c>
       <c r="J145" t="n">
-        <v>-14.326</v>
+        <v>-9.8325</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.4</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8081</v>
+        <v>-0.5558</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.3539</v>
+        <v>-10.5602</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>2.71</v>
       </c>
       <c r="I147" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J147" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.8</v>
       </c>
       <c r="I148" t="n">
-        <v>1.6346</v>
+        <v>1.4319</v>
       </c>
       <c r="J148" t="n">
-        <v>31.0574</v>
+        <v>27.2061</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.45</v>
       </c>
       <c r="I149" t="n">
-        <v>0.9169</v>
+        <v>1.0288</v>
       </c>
       <c r="J149" t="n">
-        <v>17.4211</v>
+        <v>19.5472</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>1.05</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.013</v>
+        <v>0.0775</v>
       </c>
       <c r="J150" t="n">
-        <v>-0.247</v>
+        <v>1.4725</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.7</v>
       </c>
       <c r="I151" t="n">
-        <v>-1.0066</v>
+        <v>-0.985</v>
       </c>
       <c r="J151" t="n">
-        <v>-19.1254</v>
+        <v>-18.715</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>1.044</v>
+        <v>1.0096</v>
       </c>
       <c r="J152" t="n">
-        <v>30.276</v>
+        <v>29.2784</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6735</v>
+        <v>0.6258</v>
       </c>
       <c r="J153" t="n">
-        <v>19.5315</v>
+        <v>18.1482</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2968</v>
+        <v>-0.2572</v>
       </c>
       <c r="J154" t="n">
-        <v>-8.607200000000001</v>
+        <v>-7.4588</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3604</v>
+        <v>-0.3169</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.4516</v>
+        <v>-9.190099999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.2255</v>
+        <v>-1.2308</v>
       </c>
       <c r="J156" t="n">
-        <v>-35.5395</v>
+        <v>-35.6932</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.33</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5233</v>
+        <v>0.6314</v>
       </c>
       <c r="J157" t="n">
-        <v>15.1757</v>
+        <v>18.3106</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.23</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3886</v>
+        <v>0.4621</v>
       </c>
       <c r="J158" t="n">
-        <v>11.2694</v>
+        <v>13.4009</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0936</v>
+        <v>0.1453</v>
       </c>
       <c r="J159" t="n">
-        <v>2.7144</v>
+        <v>4.2137</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.01</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0145</v>
+        <v>0.0207</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.4205</v>
+        <v>0.6002999999999999</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.92</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2232</v>
+        <v>-0.1235</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.4728</v>
+        <v>-3.5815</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.2</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4332</v>
+        <v>0.4939</v>
       </c>
       <c r="J162" t="n">
-        <v>10.83</v>
+        <v>12.3475</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>0.8</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.3424</v>
+        <v>-0.2224</v>
       </c>
       <c r="J163" t="n">
-        <v>-8.56</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>0.8</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3424</v>
+        <v>-0.2224</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.56</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.78</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3736</v>
+        <v>-0.2421</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.34</v>
+        <v>-6.0525</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4333</v>
+        <v>-0.281</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.8325</v>
+        <v>-7.025</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9003</v>
+        <v>0.8946</v>
       </c>
       <c r="J167" t="n">
-        <v>22.5075</v>
+        <v>22.365</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.23</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6387</v>
+        <v>0.6372</v>
       </c>
       <c r="J168" t="n">
-        <v>15.9675</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.17</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4656</v>
+        <v>0.4924</v>
       </c>
       <c r="J169" t="n">
-        <v>11.64</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>1.14</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3697</v>
+        <v>0.4173</v>
       </c>
       <c r="J170" t="n">
-        <v>9.2425</v>
+        <v>10.4325</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2502</v>
+        <v>-0.1744</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.255</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>0.91</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0951</v>
+        <v>-0.0961</v>
       </c>
       <c r="J172" t="n">
-        <v>-2.1873</v>
+        <v>-2.2103</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>0.83</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2331</v>
+        <v>-0.1841</v>
       </c>
       <c r="J173" t="n">
-        <v>-5.3613</v>
+        <v>-4.2343</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>0.79</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3047</v>
+        <v>-0.2235</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.0081</v>
+        <v>-5.1405</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.78</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3291</v>
+        <v>-0.2326</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.5693</v>
+        <v>-5.3498</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6029</v>
+        <v>-0.4021</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.8667</v>
+        <v>-9.2483</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.63</v>
       </c>
       <c r="I177" t="n">
-        <v>1.438</v>
+        <v>1.2856</v>
       </c>
       <c r="J177" t="n">
-        <v>33.074</v>
+        <v>29.5688</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.31</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7681</v>
+        <v>0.7983</v>
       </c>
       <c r="J178" t="n">
-        <v>17.6663</v>
+        <v>18.3609</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.16</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3649</v>
+        <v>0.4463</v>
       </c>
       <c r="J179" t="n">
-        <v>8.3927</v>
+        <v>10.2649</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.16</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3649</v>
+        <v>0.4463</v>
       </c>
       <c r="J180" t="n">
-        <v>8.3927</v>
+        <v>10.2649</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.12</v>
       </c>
       <c r="I181" t="n">
-        <v>0.2587</v>
+        <v>0.3403</v>
       </c>
       <c r="J181" t="n">
-        <v>5.9501</v>
+        <v>7.8269</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4326/event_4326_evp_summary.xlsx
+++ b/database/event/4326/event_4326_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.522</v>
+        <v>5.3727</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8475</v>
+        <v>1.7976</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8549</v>
+        <v>1.8216</v>
       </c>
       <c r="E2" t="n">
-        <v>5.522</v>
+        <v>5.3727</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3907</v>
+        <v>3.1318</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1313</v>
+        <v>2.2409</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0855</v>
+        <v>4.1295</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4285</v>
+        <v>4.3451</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1313</v>
+        <v>2.2409</v>
       </c>
       <c r="K2" t="n">
         <v>142</v>
@@ -529,7 +529,7 @@
         <v>71</v>
       </c>
       <c r="M2" t="n">
-        <v>6.559799999999999</v>
+        <v>6.586</v>
       </c>
       <c r="N2" t="n">
         <v>213</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.9979</v>
+        <v>3.7535</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3376</v>
+        <v>1.2558</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1668</v>
+        <v>1.0845</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9979</v>
+        <v>3.7535</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9869</v>
+        <v>2.6783</v>
       </c>
       <c r="G3" t="n">
-        <v>1.011</v>
+        <v>1.0752</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1989</v>
+        <v>3.1371</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4674</v>
+        <v>3.3009</v>
       </c>
       <c r="J3" t="n">
-        <v>1.011</v>
+        <v>1.0752</v>
       </c>
       <c r="K3" t="n">
         <v>142</v>
@@ -575,7 +575,7 @@
         <v>71</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4784</v>
+        <v>4.3761</v>
       </c>
       <c r="N3" t="n">
         <v>213</v>
@@ -584,81 +584,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.0343</v>
+        <v>2.9124</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0152</v>
+        <v>0.9744</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7318</v>
+        <v>0.7016</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0343</v>
+        <v>2.9124</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8889</v>
+        <v>0.5694</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1454</v>
+        <v>2.343</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9837</v>
+        <v>0.5694</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9837</v>
+        <v>0.5991</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1454</v>
+        <v>2.343</v>
       </c>
       <c r="K4" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="L4" t="n">
         <v>71</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1291</v>
+        <v>2.9421</v>
       </c>
       <c r="N4" t="n">
-        <v>191</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.9062</v>
+        <v>2.7204</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9102</v>
       </c>
       <c r="D5" t="n">
-        <v>0.674</v>
+        <v>0.6142</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9062</v>
+        <v>2.7204</v>
       </c>
       <c r="F5" t="n">
-        <v>3.458</v>
+        <v>2.5792</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5518</v>
+        <v>0.1412</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2334</v>
+        <v>2.9201</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2334</v>
+        <v>2.9201</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5518</v>
+        <v>0.1412</v>
       </c>
       <c r="K5" t="n">
         <v>120</v>
@@ -667,7 +667,7 @@
         <v>71</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6816</v>
+        <v>3.0613</v>
       </c>
       <c r="N5" t="n">
         <v>191</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8656</v>
+        <v>2.6864</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9587</v>
+        <v>0.8988</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.5987</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8656</v>
+        <v>2.6864</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8656</v>
+        <v>3.2571</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0.5707</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9327</v>
+        <v>4.4039</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9327</v>
+        <v>4.4039</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0.5707</v>
       </c>
       <c r="K6" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9327</v>
+        <v>3.8332</v>
       </c>
       <c r="N6" t="n">
-        <v>133</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7811</v>
+        <v>2.5336</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9305</v>
+        <v>0.8477</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6175</v>
+        <v>0.5291</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7811</v>
+        <v>2.5336</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5921</v>
+        <v>2.5336</v>
       </c>
       <c r="G7" t="n">
-        <v>2.189</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5921</v>
+        <v>2.8203</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6418</v>
+        <v>2.8203</v>
       </c>
       <c r="J7" t="n">
-        <v>2.189</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="L7" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8308</v>
+        <v>2.8203</v>
       </c>
       <c r="N7" t="n">
-        <v>213</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5494</v>
+        <v>2.2255</v>
       </c>
       <c r="C8" t="n">
-        <v>0.853</v>
+        <v>0.7446</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5129</v>
+        <v>0.3889</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5494</v>
+        <v>2.2255</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3116</v>
+        <v>3.0206</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7622</v>
+        <v>-0.7951</v>
       </c>
       <c r="H8" t="n">
-        <v>3.912</v>
+        <v>3.8863</v>
       </c>
       <c r="I8" t="n">
-        <v>3.912</v>
+        <v>3.8863</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7622</v>
+        <v>-0.7951</v>
       </c>
       <c r="K8" t="n">
         <v>120</v>
@@ -805,7 +805,7 @@
         <v>71</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1498</v>
+        <v>3.0912</v>
       </c>
       <c r="N8" t="n">
         <v>191</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.0931</v>
+        <v>2.0521</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7003</v>
+        <v>0.6866</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3069</v>
+        <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0931</v>
+        <v>2.0521</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0931</v>
+        <v>2.0521</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0931</v>
+        <v>2.0521</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0931</v>
+        <v>2.0521</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0931</v>
+        <v>2.0521</v>
       </c>
       <c r="N9" t="n">
         <v>133</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0487</v>
+        <v>2.0513</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6854</v>
+        <v>0.6863</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2869</v>
+        <v>0.3096</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0487</v>
+        <v>2.0513</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2351</v>
+        <v>2.2586</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1864</v>
+        <v>-0.2073</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2351</v>
+        <v>2.2586</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2351</v>
+        <v>2.2586</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1864</v>
+        <v>-0.2073</v>
       </c>
       <c r="K10" t="n">
         <v>120</v>
@@ -897,7 +897,7 @@
         <v>71</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0487</v>
+        <v>2.0513</v>
       </c>
       <c r="N10" t="n">
         <v>191</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.9998</v>
+        <v>1.8823</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6691</v>
+        <v>0.6298</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2648</v>
+        <v>0.2327</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9998</v>
+        <v>1.8823</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9998</v>
+        <v>1.8823</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9998</v>
+        <v>1.8823</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9998</v>
+        <v>1.8823</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9998</v>
+        <v>1.8823</v>
       </c>
       <c r="N11" t="n">
         <v>133</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7602</v>
+        <v>1.7972</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5889</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1566</v>
+        <v>0.1939</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7602</v>
+        <v>1.7972</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8621</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8981</v>
+        <v>0.9358</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8621</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9345</v>
+        <v>0.9064</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8981</v>
+        <v>0.9358</v>
       </c>
       <c r="K12" t="n">
         <v>142</v>
@@ -989,7 +989,7 @@
         <v>71</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8326</v>
+        <v>1.8422</v>
       </c>
       <c r="N12" t="n">
         <v>213</v>
@@ -998,139 +998,139 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7185</v>
+        <v>1.6013</v>
       </c>
       <c r="C13" t="n">
-        <v>0.575</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1378</v>
+        <v>0.1047</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7185</v>
+        <v>1.6013</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7185</v>
+        <v>1.6606</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.0593</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7185</v>
+        <v>1.6606</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7185</v>
+        <v>1.6606</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.0593</v>
       </c>
       <c r="K13" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7185</v>
+        <v>1.6013</v>
       </c>
       <c r="N13" t="n">
-        <v>122</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5892</v>
+        <v>1.5782</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5317</v>
+        <v>0.528</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0794</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5892</v>
+        <v>1.5782</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5892</v>
+        <v>1.5782</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5892</v>
+        <v>1.5782</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5892</v>
+        <v>1.5782</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5892</v>
+        <v>1.5782</v>
       </c>
       <c r="N14" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5791</v>
+        <v>1.548</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5283</v>
+        <v>0.5179</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0805</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5791</v>
+        <v>1.548</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6157</v>
+        <v>1.548</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0366</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6157</v>
+        <v>1.548</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6157</v>
+        <v>1.548</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0366</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="L15" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5791</v>
+        <v>1.548</v>
       </c>
       <c r="N15" t="n">
-        <v>191</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0871</v>
+        <v>1.0193</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3637</v>
+        <v>0.341</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1472</v>
+        <v>-0.1602</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0871</v>
+        <v>1.0193</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0871</v>
+        <v>1.0193</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0871</v>
+        <v>1.0193</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0871</v>
+        <v>1.0193</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0871</v>
+        <v>1.0193</v>
       </c>
       <c r="N16" t="n">
         <v>128</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9105</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3046</v>
+        <v>0.2723</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.227</v>
+        <v>-0.2537</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9105</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9105</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9105</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9105</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9105</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>128</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5003</v>
+        <v>0.4508</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1674</v>
+        <v>0.1508</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4122</v>
+        <v>-0.419</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5003</v>
+        <v>0.4508</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5003</v>
+        <v>0.4508</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5003</v>
+        <v>0.4508</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5003</v>
+        <v>0.4508</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5003</v>
+        <v>0.4508</v>
       </c>
       <c r="N18" t="n">
         <v>122</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3286</v>
+        <v>0.2925</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1099</v>
+        <v>0.0979</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4897</v>
+        <v>-0.4911</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3286</v>
+        <v>0.2925</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3286</v>
+        <v>0.2925</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3286</v>
+        <v>0.2925</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3286</v>
+        <v>0.2925</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3286</v>
+        <v>0.2925</v>
       </c>
       <c r="N19" t="n">
         <v>122</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.319</v>
+        <v>0.2759</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1067</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.494</v>
+        <v>-0.4986</v>
       </c>
       <c r="E20" t="n">
-        <v>0.319</v>
+        <v>0.2759</v>
       </c>
       <c r="F20" t="n">
-        <v>0.319</v>
+        <v>0.2759</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.319</v>
+        <v>0.2759</v>
       </c>
       <c r="I20" t="n">
-        <v>0.319</v>
+        <v>0.2759</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.319</v>
+        <v>0.2759</v>
       </c>
       <c r="N20" t="n">
         <v>122</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2611</v>
+        <v>0.2069</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0692</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5201</v>
+        <v>-0.53</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2611</v>
+        <v>0.2069</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2611</v>
+        <v>0.2069</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2611</v>
+        <v>0.2069</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2611</v>
+        <v>0.2069</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2611</v>
+        <v>0.2069</v>
       </c>
       <c r="N21" t="n">
         <v>122</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1005</v>
+        <v>-0.1243</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0336</v>
+        <v>-0.0416</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6834</v>
+        <v>-0.6808</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1005</v>
+        <v>-0.1243</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1005</v>
+        <v>-0.1243</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1005</v>
+        <v>-0.1243</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1005</v>
+        <v>-0.1243</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1005</v>
+        <v>-0.1243</v>
       </c>
       <c r="N22" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.157</v>
+        <v>-0.1617</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0525</v>
+        <v>-0.0541</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7089</v>
+        <v>-0.6978</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.157</v>
+        <v>-0.1617</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.157</v>
+        <v>-0.1617</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.157</v>
+        <v>-0.1617</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.157</v>
+        <v>-0.1617</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.157</v>
+        <v>-0.1617</v>
       </c>
       <c r="N23" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3131</v>
+        <v>-0.3732</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1048</v>
+        <v>-0.1249</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7794</v>
+        <v>-0.7941</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3131</v>
+        <v>-0.3732</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3131</v>
+        <v>-0.3732</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3131</v>
+        <v>-0.3732</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3131</v>
+        <v>-0.3732</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3131</v>
+        <v>-0.3732</v>
       </c>
       <c r="N24" t="n">
         <v>125</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.4509</v>
+        <v>-0.5094</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1509</v>
+        <v>-0.1704</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8416</v>
+        <v>-0.8561</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4509</v>
+        <v>-0.5094</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4509</v>
+        <v>-0.5094</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4509</v>
+        <v>-0.5094</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4509</v>
+        <v>-0.5094</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4509</v>
+        <v>-0.5094</v>
       </c>
       <c r="N25" t="n">
         <v>128</v>
@@ -1596,78 +1596,78 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.602</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.19</v>
+        <v>-0.2014</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8944</v>
+        <v>-0.8982</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.602</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.9466</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.3446</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.9466</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.996</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.3446</v>
       </c>
       <c r="K26" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.6514</v>
       </c>
       <c r="N26" t="n">
-        <v>125</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.7774</v>
+        <v>-0.6599</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2601</v>
+        <v>-0.2208</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.989</v>
+        <v>-0.9246</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.7774</v>
+        <v>-0.6599</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.7774</v>
+        <v>-0.6599</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7774</v>
+        <v>-0.6599</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7774</v>
+        <v>-0.6599</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.7774</v>
+        <v>-0.6599</v>
       </c>
       <c r="N27" t="n">
         <v>125</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.8385</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3041</v>
+        <v>-0.2805</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0483</v>
+        <v>-1.0059</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.8385</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.1691</v>
+        <v>-0.8385</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2603</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.1691</v>
+        <v>-0.8385</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.2672</v>
+        <v>-0.8385</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2603</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="L28" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.0069</v>
+        <v>-0.8385</v>
       </c>
       <c r="N28" t="n">
-        <v>213</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.4154</v>
+        <v>-1.4906</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.4736</v>
+        <v>-0.4987</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.277</v>
+        <v>-1.3028</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.4154</v>
+        <v>-1.4906</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.4154</v>
+        <v>-1.4906</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.4154</v>
+        <v>-1.4906</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.4154</v>
+        <v>-1.4906</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.4154</v>
+        <v>-1.4906</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.7575</v>
+        <v>-1.7744</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.588</v>
+        <v>-0.5937</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.4314</v>
+        <v>-1.4319</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.7575</v>
+        <v>-1.7744</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.7575</v>
+        <v>-1.7744</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.7575</v>
+        <v>-1.7744</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.7575</v>
+        <v>-1.7744</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.7575</v>
+        <v>-1.7744</v>
       </c>
       <c r="N30" t="n">
         <v>128</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.0745</v>
+        <v>-2.0618</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.6898</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.5745</v>
+        <v>-1.5628</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.0745</v>
+        <v>-2.0618</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.0745</v>
+        <v>-2.0618</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.0745</v>
+        <v>-2.0618</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.0745</v>
+        <v>-2.0618</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.0745</v>
+        <v>-2.0618</v>
       </c>
       <c r="N31" t="n">
         <v>128</v>
@@ -1969,10 +1969,10 @@
         <v>1.24</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4001</v>
+        <v>0.3989</v>
       </c>
       <c r="J2" t="n">
-        <v>11.6029</v>
+        <v>11.5681</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1792</v>
+        <v>0.187</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1968</v>
+        <v>5.423</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0339</v>
+        <v>-0.0411</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9831</v>
+        <v>-1.1919</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1525</v>
+        <v>-0.1665</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.4225</v>
+        <v>-4.8285</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.65</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3796</v>
+        <v>-0.3902</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.0084</v>
+        <v>-11.3158</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.21</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3065</v>
+        <v>0.3205</v>
       </c>
       <c r="J7" t="n">
-        <v>8.888500000000001</v>
+        <v>9.294499999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2684</v>
+        <v>0.2834</v>
       </c>
       <c r="J8" t="n">
-        <v>7.7836</v>
+        <v>8.2186</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2031</v>
+        <v>0.2188</v>
       </c>
       <c r="J9" t="n">
-        <v>5.8899</v>
+        <v>6.3452</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1349</v>
+        <v>0.1496</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9121</v>
+        <v>4.3384</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1667</v>
+        <v>-0.1776</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.8343</v>
+        <v>-5.1504</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>1.205</v>
+        <v>1.2285</v>
       </c>
       <c r="J12" t="n">
-        <v>28.92</v>
+        <v>29.484</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3677</v>
+        <v>0.368</v>
       </c>
       <c r="J13" t="n">
-        <v>8.8248</v>
+        <v>8.832000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3677</v>
+        <v>0.368</v>
       </c>
       <c r="J14" t="n">
-        <v>8.8248</v>
+        <v>8.832000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.03</v>
       </c>
       <c r="I15" t="n">
-        <v>0.096</v>
+        <v>0.1122</v>
       </c>
       <c r="J15" t="n">
-        <v>2.304</v>
+        <v>2.6928</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.96</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2052</v>
+        <v>-0.1971</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.9248</v>
+        <v>-4.7304</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2073</v>
+        <v>0.2088</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9752</v>
+        <v>5.0112</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>0.95</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0805</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6464</v>
+        <v>-1.932</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0808</v>
+        <v>-0.0934</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9392</v>
+        <v>-2.2416</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1038</v>
+        <v>-0.1176</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4912</v>
+        <v>-2.8224</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3355</v>
+        <v>-0.3488</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.052</v>
+        <v>-8.3712</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.99</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6421</v>
+        <v>1.788</v>
       </c>
       <c r="J22" t="n">
-        <v>29.5578</v>
+        <v>32.184</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.74</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3635</v>
+        <v>1.474</v>
       </c>
       <c r="J23" t="n">
-        <v>24.543</v>
+        <v>26.532</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.64</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2501</v>
+        <v>1.3134</v>
       </c>
       <c r="J24" t="n">
-        <v>22.5018</v>
+        <v>23.6412</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.58</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1817</v>
+        <v>1.2138</v>
       </c>
       <c r="J25" t="n">
-        <v>21.2706</v>
+        <v>21.8484</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.78</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7922</v>
+        <v>-0.7174</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.2596</v>
+        <v>-12.9132</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.76</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2242</v>
+        <v>-0.2493</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.0356</v>
+        <v>-4.4874</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.7</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2857</v>
+        <v>-0.3085</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.1426</v>
+        <v>-5.553</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.63</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3512</v>
+        <v>-0.3715</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.3216</v>
+        <v>-6.687</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.61</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3684</v>
+        <v>-0.3881</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.6312</v>
+        <v>-6.9858</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.44</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5269</v>
+        <v>-0.537</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.4842</v>
+        <v>-9.666</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2254</v>
+        <v>0.2323</v>
       </c>
       <c r="J32" t="n">
-        <v>6.762</v>
+        <v>6.969</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1613</v>
+        <v>0.1698</v>
       </c>
       <c r="J33" t="n">
-        <v>4.839</v>
+        <v>5.094</v>
       </c>
     </row>
     <row r="34">
@@ -3289,10 +3289,10 @@
         <v>0.96</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0634</v>
+        <v>-0.0727</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.902</v>
+        <v>-2.181</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.9</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1345</v>
+        <v>-0.1471</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.035</v>
+        <v>-4.413</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.28</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5427</v>
+        <v>0.5367</v>
       </c>
       <c r="J37" t="n">
-        <v>16.281</v>
+        <v>16.101</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4057</v>
+        <v>0.4097</v>
       </c>
       <c r="J38" t="n">
-        <v>12.171</v>
+        <v>12.291</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.16</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3349</v>
+        <v>0.343</v>
       </c>
       <c r="J39" t="n">
-        <v>10.047</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.06</v>
       </c>
       <c r="I40" t="n">
-        <v>0.142</v>
+        <v>0.1561</v>
       </c>
       <c r="J40" t="n">
-        <v>4.26</v>
+        <v>4.683</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.95</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.0965</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.682</v>
+        <v>-2.895</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9067</v>
+        <v>0.8524</v>
       </c>
       <c r="J42" t="n">
-        <v>26.2943</v>
+        <v>24.7196</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.31</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8159</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>23.6611</v>
+        <v>22.4083</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.25</v>
       </c>
       <c r="I44" t="n">
-        <v>0.677</v>
+        <v>0.6501</v>
       </c>
       <c r="J44" t="n">
-        <v>19.633</v>
+        <v>18.8529</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.07</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2144</v>
+        <v>0.2283</v>
       </c>
       <c r="J45" t="n">
-        <v>6.2176</v>
+        <v>6.6207</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.1038</v>
       </c>
       <c r="J46" t="n">
-        <v>2.436</v>
+        <v>3.0102</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.2</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4673</v>
+        <v>0.4547</v>
       </c>
       <c r="J47" t="n">
-        <v>13.5517</v>
+        <v>13.1863</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>0.135</v>
+        <v>0.1383</v>
       </c>
       <c r="J48" t="n">
-        <v>3.915</v>
+        <v>4.0107</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1891</v>
+        <v>-0.2048</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.4839</v>
+        <v>-5.9392</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.78</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2495</v>
+        <v>-0.2647</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.2355</v>
+        <v>-7.6763</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.75</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2789</v>
+        <v>-0.2936</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.088100000000001</v>
+        <v>-8.5144</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.2</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4362</v>
+        <v>0.4319</v>
       </c>
       <c r="J52" t="n">
-        <v>12.6498</v>
+        <v>12.5251</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2444</v>
+        <v>0.2511</v>
       </c>
       <c r="J53" t="n">
-        <v>7.0876</v>
+        <v>7.2819</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2031</v>
+        <v>0.2111</v>
       </c>
       <c r="J54" t="n">
-        <v>5.8899</v>
+        <v>6.1219</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.91</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1239</v>
+        <v>-0.1361</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.5931</v>
+        <v>-3.9469</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2892</v>
+        <v>-0.3017</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.386799999999999</v>
+        <v>-8.7493</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.33</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8809</v>
+        <v>0.8262</v>
       </c>
       <c r="J57" t="n">
-        <v>25.5461</v>
+        <v>23.9598</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.18</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5214</v>
+        <v>0.508</v>
       </c>
       <c r="J58" t="n">
-        <v>15.1206</v>
+        <v>14.732</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.15</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4464</v>
+        <v>0.4399</v>
       </c>
       <c r="J59" t="n">
-        <v>12.9456</v>
+        <v>12.7571</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1332</v>
+        <v>0.1475</v>
       </c>
       <c r="J60" t="n">
-        <v>3.8628</v>
+        <v>4.2775</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>1.02</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0615</v>
+        <v>0.0775</v>
       </c>
       <c r="J61" t="n">
-        <v>1.7835</v>
+        <v>2.2475</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.88</v>
       </c>
       <c r="I62" t="n">
-        <v>1.6141</v>
+        <v>1.6033</v>
       </c>
       <c r="J62" t="n">
-        <v>45.1948</v>
+        <v>44.8924</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7489</v>
+        <v>0.7134</v>
       </c>
       <c r="J63" t="n">
-        <v>20.9692</v>
+        <v>19.9752</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.03</v>
       </c>
       <c r="I64" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1052</v>
       </c>
       <c r="J64" t="n">
-        <v>2.408</v>
+        <v>2.9456</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.95</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2489</v>
+        <v>-0.2362</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.9692</v>
+        <v>-6.6136</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.83</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5952</v>
+        <v>-0.5543</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.6656</v>
+        <v>-15.5204</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.28</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6394</v>
+        <v>0.6078</v>
       </c>
       <c r="J67" t="n">
-        <v>17.9032</v>
+        <v>17.0184</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.06</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1986</v>
+        <v>0.1969</v>
       </c>
       <c r="J68" t="n">
-        <v>5.5608</v>
+        <v>5.5132</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.83</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1937</v>
+        <v>-0.2106</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.4236</v>
+        <v>-5.8968</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.63</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3868</v>
+        <v>-0.3991</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.8304</v>
+        <v>-11.1748</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.57</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4425</v>
+        <v>-0.4522</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.39</v>
+        <v>-12.6616</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.58</v>
       </c>
       <c r="I72" t="n">
-        <v>1.2264</v>
+        <v>1.1981</v>
       </c>
       <c r="J72" t="n">
-        <v>30.66</v>
+        <v>29.9525</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8448</v>
+        <v>0.8011</v>
       </c>
       <c r="J73" t="n">
-        <v>21.12</v>
+        <v>20.0275</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.23</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.6018</v>
       </c>
       <c r="J74" t="n">
-        <v>15.5125</v>
+        <v>15.045</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.12</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3426</v>
+        <v>0.3506</v>
       </c>
       <c r="J75" t="n">
-        <v>8.565</v>
+        <v>8.765000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.07</v>
       </c>
       <c r="I76" t="n">
-        <v>0.199</v>
+        <v>0.2176</v>
       </c>
       <c r="J76" t="n">
-        <v>4.975</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1064</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>2.66</v>
+        <v>2.3325</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.89</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1189</v>
+        <v>-0.138</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.9725</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1939</v>
+        <v>-0.2132</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.8475</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.62</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3831</v>
+        <v>-0.3978</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.577500000000001</v>
+        <v>-9.945</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4391</v>
+        <v>-0.451</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.9775</v>
+        <v>-11.275</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>0.7</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.2561</v>
+        <v>-0.2853</v>
       </c>
       <c r="J82" t="n">
-        <v>-4.6098</v>
+        <v>-5.1354</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>0.55</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.4078</v>
+        <v>-0.4283</v>
       </c>
       <c r="J83" t="n">
-        <v>-7.3404</v>
+        <v>-7.7094</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.54</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.4167</v>
+        <v>-0.4367</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.5006</v>
+        <v>-7.8606</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.44</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5078</v>
+        <v>-0.522</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.1404</v>
+        <v>-9.396000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.43</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5174</v>
+        <v>-0.5309</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.3132</v>
+        <v>-9.5562</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.74</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3559</v>
+        <v>1.3474</v>
       </c>
       <c r="J87" t="n">
-        <v>24.4062</v>
+        <v>24.2532</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.65</v>
       </c>
       <c r="I88" t="n">
-        <v>1.2555</v>
+        <v>1.2399</v>
       </c>
       <c r="J88" t="n">
-        <v>22.599</v>
+        <v>22.3182</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.61</v>
       </c>
       <c r="I89" t="n">
-        <v>1.2112</v>
+        <v>1.192</v>
       </c>
       <c r="J89" t="n">
-        <v>21.8016</v>
+        <v>21.456</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>1.58</v>
       </c>
       <c r="I90" t="n">
-        <v>1.1781</v>
+        <v>1.1561</v>
       </c>
       <c r="J90" t="n">
-        <v>21.2058</v>
+        <v>20.8098</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>1.44</v>
       </c>
       <c r="I91" t="n">
-        <v>1.0062</v>
+        <v>0.964</v>
       </c>
       <c r="J91" t="n">
-        <v>18.1116</v>
+        <v>17.352</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.84</v>
       </c>
       <c r="I92" t="n">
-        <v>1.5377</v>
+        <v>1.5278</v>
       </c>
       <c r="J92" t="n">
-        <v>39.9802</v>
+        <v>39.7228</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.33</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.7993</v>
       </c>
       <c r="J93" t="n">
-        <v>21.8972</v>
+        <v>20.7818</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.22</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5946</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="J94" t="n">
-        <v>15.4596</v>
+        <v>15.0566</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1653</v>
+        <v>0.1866</v>
       </c>
       <c r="J95" t="n">
-        <v>4.2978</v>
+        <v>4.8516</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3016</v>
+        <v>-0.281</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.8416</v>
+        <v>-7.306</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2674</v>
+        <v>0.2581</v>
       </c>
       <c r="J97" t="n">
-        <v>6.9524</v>
+        <v>6.7106</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>0.86</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1583</v>
+        <v>-0.1762</v>
       </c>
       <c r="J98" t="n">
-        <v>-4.1158</v>
+        <v>-4.5812</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>0.78</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2366</v>
+        <v>-0.2547</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.1516</v>
+        <v>-6.6222</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.72</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2943</v>
+        <v>-0.3113</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.6518</v>
+        <v>-8.0938</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.66</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3513</v>
+        <v>-0.3663</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.133800000000001</v>
+        <v>-9.5238</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.54</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1781</v>
+        <v>1.1462</v>
       </c>
       <c r="J102" t="n">
-        <v>28.2744</v>
+        <v>27.5088</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7792</v>
+        <v>0.7431</v>
       </c>
       <c r="J103" t="n">
-        <v>18.7008</v>
+        <v>17.8344</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.23</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6216</v>
+        <v>0.6025</v>
       </c>
       <c r="J104" t="n">
-        <v>14.9184</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.14</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3977</v>
+        <v>0.4007</v>
       </c>
       <c r="J105" t="n">
-        <v>9.5448</v>
+        <v>9.6168</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>1.09</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2597</v>
+        <v>0.2739</v>
       </c>
       <c r="J106" t="n">
-        <v>6.2328</v>
+        <v>6.5736</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.03</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1489</v>
+        <v>0.1415</v>
       </c>
       <c r="J107" t="n">
-        <v>3.5736</v>
+        <v>3.396</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>0.88</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.136</v>
+        <v>-0.1539</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.264</v>
+        <v>-3.6936</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1881</v>
+        <v>-0.2064</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.5144</v>
+        <v>-4.9536</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.7</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3125</v>
+        <v>-0.3291</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.5</v>
+        <v>-7.8984</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.63</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3786</v>
+        <v>-0.3927</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.086399999999999</v>
+        <v>-9.424799999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1557</v>
+        <v>1.1216</v>
       </c>
       <c r="J112" t="n">
-        <v>26.5811</v>
+        <v>25.7968</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.4</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9932</v>
+        <v>0.9384</v>
       </c>
       <c r="J113" t="n">
-        <v>22.8436</v>
+        <v>21.5832</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.9153</v>
+        <v>0.8625</v>
       </c>
       <c r="J114" t="n">
-        <v>21.0519</v>
+        <v>19.8375</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3738</v>
+        <v>0.3783</v>
       </c>
       <c r="J115" t="n">
-        <v>8.5974</v>
+        <v>8.700900000000001</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.83</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.608</v>
+        <v>-0.5633</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.984</v>
+        <v>-12.9559</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.24</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5502</v>
+        <v>0.5294</v>
       </c>
       <c r="J117" t="n">
-        <v>12.6546</v>
+        <v>12.1762</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1646</v>
+        <v>0.1662</v>
       </c>
       <c r="J118" t="n">
-        <v>3.7858</v>
+        <v>3.8226</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.92</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.103</v>
+        <v>-0.117</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.369</v>
+        <v>-2.691</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.76</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2668</v>
+        <v>-0.2822</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.1364</v>
+        <v>-6.4906</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4644</v>
+        <v>-0.4724</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.6812</v>
+        <v>-10.8652</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1633</v>
+        <v>1.1235</v>
       </c>
       <c r="J122" t="n">
-        <v>34.899</v>
+        <v>33.705</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.32</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8666</v>
+        <v>0.8121</v>
       </c>
       <c r="J123" t="n">
-        <v>25.998</v>
+        <v>24.363</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.23</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6511</v>
+        <v>0.6227</v>
       </c>
       <c r="J124" t="n">
-        <v>19.533</v>
+        <v>18.681</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3534</v>
+        <v>-0.3386</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.602</v>
+        <v>-10.158</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.64</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.0504</v>
+        <v>-0.957</v>
       </c>
       <c r="J126" t="n">
-        <v>-31.512</v>
+        <v>-28.71</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2962</v>
+        <v>0.2979</v>
       </c>
       <c r="J127" t="n">
-        <v>8.885999999999999</v>
+        <v>8.936999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.005</v>
+        <v>0.0035</v>
       </c>
       <c r="J128" t="n">
-        <v>0.15</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.99</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0182</v>
+        <v>-0.0235</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.546</v>
+        <v>-0.705</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.91</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1194</v>
+        <v>-0.1326</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.582</v>
+        <v>-3.978</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2249</v>
+        <v>-0.2393</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.747</v>
+        <v>-7.179</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.76</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4878</v>
+        <v>1.468</v>
       </c>
       <c r="J132" t="n">
-        <v>40.1706</v>
+        <v>39.636</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.47</v>
       </c>
       <c r="I133" t="n">
-        <v>1.1182</v>
+        <v>1.0761</v>
       </c>
       <c r="J133" t="n">
-        <v>30.1914</v>
+        <v>29.0547</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.97</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1665</v>
+        <v>-0.1607</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.4955</v>
+        <v>-4.3389</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6603</v>
+        <v>-0.6149</v>
       </c>
       <c r="J135" t="n">
-        <v>-17.8281</v>
+        <v>-16.6023</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.7</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>-24.5916</v>
+        <v>-22.5504</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.494</v>
+        <v>0.4779</v>
       </c>
       <c r="J137" t="n">
-        <v>13.338</v>
+        <v>12.9033</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0926</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.1519</v>
+        <v>-2.5002</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.9</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1245</v>
+        <v>-0.1395</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.3615</v>
+        <v>-3.7665</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.76</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2668</v>
+        <v>-0.2822</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.2036</v>
+        <v>-7.6194</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3151</v>
+        <v>-0.3294</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.5077</v>
+        <v>-8.893800000000001</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.1513</v>
+        <v>-0.182</v>
       </c>
       <c r="J142" t="n">
-        <v>-2.8747</v>
+        <v>-3.458</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>0.64</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.3329</v>
+        <v>-0.3557</v>
       </c>
       <c r="J143" t="n">
-        <v>-6.3251</v>
+        <v>-6.7583</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.6</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3708</v>
+        <v>-0.3917</v>
       </c>
       <c r="J144" t="n">
-        <v>-7.0452</v>
+        <v>-7.4423</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.44</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5175</v>
+        <v>-0.5296</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.8325</v>
+        <v>-10.0624</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.4</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5558</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.5602</v>
+        <v>-10.735</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>2.71</v>
       </c>
       <c r="I147" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J147" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.8</v>
       </c>
       <c r="I148" t="n">
-        <v>1.4319</v>
+        <v>1.4264</v>
       </c>
       <c r="J148" t="n">
-        <v>27.2061</v>
+        <v>27.1016</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.45</v>
       </c>
       <c r="I149" t="n">
-        <v>1.0288</v>
+        <v>0.9872</v>
       </c>
       <c r="J149" t="n">
-        <v>19.5472</v>
+        <v>18.7568</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>1.05</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0775</v>
+        <v>0.117</v>
       </c>
       <c r="J150" t="n">
-        <v>1.4725</v>
+        <v>2.223</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.7</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.985</v>
+        <v>-0.8878</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.715</v>
+        <v>-16.8682</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>1.0096</v>
+        <v>0.9387</v>
       </c>
       <c r="J152" t="n">
-        <v>29.2784</v>
+        <v>27.2223</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6258</v>
+        <v>0.5907</v>
       </c>
       <c r="J153" t="n">
-        <v>18.1482</v>
+        <v>17.1303</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2572</v>
+        <v>-0.2576</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.4588</v>
+        <v>-7.4704</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3169</v>
+        <v>-0.3132</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.190099999999999</v>
+        <v>-9.082800000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.2308</v>
+        <v>-1.1163</v>
       </c>
       <c r="J156" t="n">
-        <v>-35.6932</v>
+        <v>-32.3727</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.33</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6314</v>
+        <v>0.6168</v>
       </c>
       <c r="J157" t="n">
-        <v>18.3106</v>
+        <v>17.8872</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.23</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4621</v>
+        <v>0.4614</v>
       </c>
       <c r="J158" t="n">
-        <v>13.4009</v>
+        <v>13.3806</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1453</v>
+        <v>0.1585</v>
       </c>
       <c r="J159" t="n">
-        <v>4.2137</v>
+        <v>4.5965</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.01</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0207</v>
+        <v>0.0312</v>
       </c>
       <c r="J160" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.9048</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.92</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1235</v>
+        <v>-0.1328</v>
       </c>
       <c r="J161" t="n">
-        <v>-3.5815</v>
+        <v>-3.8512</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.2</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4939</v>
+        <v>0.4744</v>
       </c>
       <c r="J162" t="n">
-        <v>12.3475</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>0.8</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2224</v>
+        <v>-0.2395</v>
       </c>
       <c r="J163" t="n">
-        <v>-5.56</v>
+        <v>-5.9875</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>0.8</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2224</v>
+        <v>-0.2395</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.56</v>
+        <v>-5.9875</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.78</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2421</v>
+        <v>-0.259</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.0525</v>
+        <v>-6.475</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.281</v>
+        <v>-0.2972</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.025</v>
+        <v>-7.43</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8946</v>
+        <v>0.8398</v>
       </c>
       <c r="J167" t="n">
-        <v>22.365</v>
+        <v>20.995</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.23</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6372</v>
+        <v>0.6131</v>
       </c>
       <c r="J168" t="n">
-        <v>15.93</v>
+        <v>15.3275</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.17</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4924</v>
+        <v>0.4827</v>
       </c>
       <c r="J169" t="n">
-        <v>12.31</v>
+        <v>12.0675</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>1.14</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4173</v>
+        <v>0.4141</v>
       </c>
       <c r="J170" t="n">
-        <v>10.4325</v>
+        <v>10.3525</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1744</v>
+        <v>-0.1662</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.36</v>
+        <v>-4.155</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>0.91</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0961</v>
+        <v>-0.1147</v>
       </c>
       <c r="J172" t="n">
-        <v>-2.2103</v>
+        <v>-2.6381</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>0.83</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1841</v>
+        <v>-0.2033</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.2343</v>
+        <v>-4.6759</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>0.79</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2235</v>
+        <v>-0.2426</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.1405</v>
+        <v>-5.5798</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.78</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2326</v>
+        <v>-0.2517</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.3498</v>
+        <v>-5.7891</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4021</v>
+        <v>-0.4159</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.2483</v>
+        <v>-9.5657</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.63</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2856</v>
+        <v>1.2616</v>
       </c>
       <c r="J177" t="n">
-        <v>29.5688</v>
+        <v>29.0168</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.31</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7983</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>18.3609</v>
+        <v>17.4938</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.16</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4463</v>
+        <v>0.4456</v>
       </c>
       <c r="J179" t="n">
-        <v>10.2649</v>
+        <v>10.2488</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.16</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4463</v>
+        <v>0.4456</v>
       </c>
       <c r="J180" t="n">
-        <v>10.2649</v>
+        <v>10.2488</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.12</v>
       </c>
       <c r="I181" t="n">
-        <v>0.3403</v>
+        <v>0.349</v>
       </c>
       <c r="J181" t="n">
-        <v>7.8269</v>
+        <v>8.026999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4326/event_4326_evp_summary.xlsx
+++ b/database/event/4326/event_4326_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3727</v>
+        <v>5.3131</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7976</v>
+        <v>1.7776</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8216</v>
+        <v>1.8146</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3727</v>
+        <v>5.3131</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1318</v>
+        <v>3.0737</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2409</v>
+        <v>2.2394</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1295</v>
+        <v>4.0939</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3451</v>
+        <v>4.3156</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2409</v>
+        <v>2.2394</v>
       </c>
       <c r="K2" t="n">
         <v>142</v>
@@ -529,7 +529,7 @@
         <v>71</v>
       </c>
       <c r="M2" t="n">
-        <v>6.586</v>
+        <v>6.555</v>
       </c>
       <c r="N2" t="n">
         <v>213</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7535</v>
+        <v>3.758</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2558</v>
+        <v>1.2573</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0845</v>
+        <v>1.1062</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7535</v>
+        <v>3.758</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6783</v>
+        <v>2.6023</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0752</v>
+        <v>1.1557</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1371</v>
+        <v>3.0136</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3009</v>
+        <v>3.1768</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0752</v>
+        <v>1.1557</v>
       </c>
       <c r="K3" t="n">
         <v>142</v>
@@ -575,7 +575,7 @@
         <v>71</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3761</v>
+        <v>4.3325</v>
       </c>
       <c r="N3" t="n">
         <v>213</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.9124</v>
+        <v>2.9603</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9744</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7016</v>
+        <v>0.7428</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9124</v>
+        <v>2.9603</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5694</v>
+        <v>0.6311</v>
       </c>
       <c r="G4" t="n">
-        <v>2.343</v>
+        <v>2.3292</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5694</v>
+        <v>0.6311</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5991</v>
+        <v>0.6653</v>
       </c>
       <c r="J4" t="n">
-        <v>2.343</v>
+        <v>2.3292</v>
       </c>
       <c r="K4" t="n">
         <v>142</v>
@@ -621,7 +621,7 @@
         <v>71</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9421</v>
+        <v>2.9945</v>
       </c>
       <c r="N4" t="n">
         <v>213</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.7204</v>
+        <v>2.6152</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9102</v>
+        <v>0.875</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6142</v>
+        <v>0.5856</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7204</v>
+        <v>2.6152</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5792</v>
+        <v>3.1957</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1412</v>
+        <v>-0.5805</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9201</v>
+        <v>4.3735</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9201</v>
+        <v>4.3735</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1412</v>
+        <v>-0.5805</v>
       </c>
       <c r="K5" t="n">
         <v>120</v>
@@ -667,7 +667,7 @@
         <v>71</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0613</v>
+        <v>3.793</v>
       </c>
       <c r="N5" t="n">
         <v>191</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.6864</v>
+        <v>2.5652</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8988</v>
+        <v>0.8582</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5987</v>
+        <v>0.5628</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6864</v>
+        <v>2.5652</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2571</v>
+        <v>2.5142</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5707</v>
+        <v>0.0509</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4039</v>
+        <v>2.8117</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4039</v>
+        <v>2.8117</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5707</v>
+        <v>0.0509</v>
       </c>
       <c r="K6" t="n">
         <v>120</v>
@@ -713,7 +713,7 @@
         <v>71</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8332</v>
+        <v>2.8626</v>
       </c>
       <c r="N6" t="n">
         <v>191</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5336</v>
+        <v>2.4493</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8477</v>
+        <v>0.8195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5291</v>
+        <v>0.51</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5336</v>
+        <v>2.4493</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5336</v>
+        <v>2.4493</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8203</v>
+        <v>2.6629</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8203</v>
+        <v>2.6629</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8203</v>
+        <v>2.6629</v>
       </c>
       <c r="N7" t="n">
         <v>133</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2255</v>
+        <v>2.1881</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7446</v>
+        <v>0.7321</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3889</v>
+        <v>0.391</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2255</v>
+        <v>2.1881</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0206</v>
+        <v>2.9519</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7951</v>
+        <v>-0.7638</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8863</v>
+        <v>3.8147</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8863</v>
+        <v>3.8147</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7951</v>
+        <v>-0.7638</v>
       </c>
       <c r="K8" t="n">
         <v>120</v>
@@ -805,7 +805,7 @@
         <v>71</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0912</v>
+        <v>3.0509</v>
       </c>
       <c r="N8" t="n">
         <v>191</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.0521</v>
+        <v>1.9722</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6866</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.31</v>
+        <v>0.2926</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0521</v>
+        <v>1.9722</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0521</v>
+        <v>1.9722</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0521</v>
+        <v>1.9722</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0521</v>
+        <v>1.9722</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0521</v>
+        <v>1.9722</v>
       </c>
       <c r="N9" t="n">
         <v>133</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0513</v>
+        <v>1.9508</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6863</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3096</v>
+        <v>0.2829</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0513</v>
+        <v>1.9508</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2586</v>
+        <v>2.1756</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2073</v>
+        <v>-0.2248</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2586</v>
+        <v>2.1756</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2586</v>
+        <v>2.1756</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2073</v>
+        <v>-0.2248</v>
       </c>
       <c r="K10" t="n">
         <v>120</v>
@@ -897,7 +897,7 @@
         <v>71</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0513</v>
+        <v>1.9508</v>
       </c>
       <c r="N10" t="n">
         <v>191</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8823</v>
+        <v>1.8349</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6298</v>
+        <v>0.6139</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2327</v>
+        <v>0.2301</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8823</v>
+        <v>1.8349</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8823</v>
+        <v>1.8349</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8823</v>
+        <v>1.8349</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8823</v>
+        <v>1.8349</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8823</v>
+        <v>1.8349</v>
       </c>
       <c r="N11" t="n">
         <v>133</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7972</v>
+        <v>1.8077</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.6048</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1939</v>
+        <v>0.2177</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7972</v>
+        <v>1.8077</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8551</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9358</v>
+        <v>0.9526</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8551</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9064</v>
+        <v>0.9014</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9358</v>
+        <v>0.9526</v>
       </c>
       <c r="K12" t="n">
         <v>142</v>
@@ -989,7 +989,7 @@
         <v>71</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8422</v>
+        <v>1.854</v>
       </c>
       <c r="N12" t="n">
         <v>213</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6013</v>
+        <v>1.6264</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.5441</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1047</v>
+        <v>0.1351</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6013</v>
+        <v>1.6264</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6606</v>
+        <v>1.6264</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0593</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6606</v>
+        <v>1.6264</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6606</v>
+        <v>1.6264</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0593</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L13" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6013</v>
+        <v>1.6264</v>
       </c>
       <c r="N13" t="n">
-        <v>191</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5782</v>
+        <v>1.5795</v>
       </c>
       <c r="C14" t="n">
-        <v>0.528</v>
+        <v>0.5285</v>
       </c>
       <c r="D14" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.1137</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5782</v>
+        <v>1.5795</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5782</v>
+        <v>1.6638</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.0843</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5782</v>
+        <v>1.6638</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5782</v>
+        <v>1.6638</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.0843</v>
       </c>
       <c r="K14" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5782</v>
+        <v>1.5795</v>
       </c>
       <c r="N14" t="n">
-        <v>122</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.548</v>
+        <v>1.5284</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5179</v>
+        <v>0.5114</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0805</v>
+        <v>0.0905</v>
       </c>
       <c r="E15" t="n">
-        <v>1.548</v>
+        <v>1.5284</v>
       </c>
       <c r="F15" t="n">
-        <v>1.548</v>
+        <v>1.5284</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.548</v>
+        <v>1.5284</v>
       </c>
       <c r="I15" t="n">
-        <v>1.548</v>
+        <v>1.5284</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.548</v>
+        <v>1.5284</v>
       </c>
       <c r="N15" t="n">
         <v>133</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0193</v>
+        <v>1.071</v>
       </c>
       <c r="C16" t="n">
-        <v>0.341</v>
+        <v>0.3583</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1602</v>
+        <v>-0.1179</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0193</v>
+        <v>1.071</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0193</v>
+        <v>1.071</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0193</v>
+        <v>1.071</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0193</v>
+        <v>1.071</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0193</v>
+        <v>1.071</v>
       </c>
       <c r="N16" t="n">
         <v>128</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8083</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2723</v>
+        <v>0.2704</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2537</v>
+        <v>-0.2376</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8083</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8083</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8083</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8083</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8083</v>
       </c>
       <c r="N17" t="n">
         <v>128</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4508</v>
+        <v>0.3274</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1508</v>
+        <v>0.1095</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.419</v>
+        <v>-0.4566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4508</v>
+        <v>0.3274</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4508</v>
+        <v>0.3274</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4508</v>
+        <v>0.3274</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4508</v>
+        <v>0.3274</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4508</v>
+        <v>0.3274</v>
       </c>
       <c r="N18" t="n">
         <v>122</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2925</v>
+        <v>0.1971</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0979</v>
+        <v>0.0659</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4911</v>
+        <v>-0.516</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2925</v>
+        <v>0.1971</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2925</v>
+        <v>0.1971</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2925</v>
+        <v>0.1971</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2925</v>
+        <v>0.1971</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2925</v>
+        <v>0.1971</v>
       </c>
       <c r="N19" t="n">
         <v>122</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2759</v>
+        <v>0.1811</v>
       </c>
       <c r="C20" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0606</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4986</v>
+        <v>-0.5233</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2759</v>
+        <v>0.1811</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2759</v>
+        <v>0.1811</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2759</v>
+        <v>0.1811</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2759</v>
+        <v>0.1811</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2759</v>
+        <v>0.1811</v>
       </c>
       <c r="N20" t="n">
         <v>122</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2069</v>
+        <v>0.1374</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0692</v>
+        <v>0.046</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.53</v>
+        <v>-0.5432</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2069</v>
+        <v>0.1374</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2069</v>
+        <v>0.1374</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2069</v>
+        <v>0.1374</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2069</v>
+        <v>0.1374</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2069</v>
+        <v>0.1374</v>
       </c>
       <c r="N21" t="n">
         <v>122</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1243</v>
+        <v>-0.0881</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0416</v>
+        <v>-0.0295</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6808</v>
+        <v>-0.6459</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1243</v>
+        <v>-0.0881</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1243</v>
+        <v>-0.0881</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1243</v>
+        <v>-0.0881</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1243</v>
+        <v>-0.0881</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1243</v>
+        <v>-0.0881</v>
       </c>
       <c r="N22" t="n">
         <v>133</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1617</v>
+        <v>-0.234</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0541</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6978</v>
+        <v>-0.7124</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1617</v>
+        <v>-0.234</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1617</v>
+        <v>-0.234</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1617</v>
+        <v>-0.234</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1617</v>
+        <v>-0.234</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1617</v>
+        <v>-0.234</v>
       </c>
       <c r="N23" t="n">
         <v>125</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3732</v>
+        <v>-0.4413</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1249</v>
+        <v>-0.1476</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7941</v>
+        <v>-0.8068</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3732</v>
+        <v>-0.4413</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3732</v>
+        <v>-0.4413</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3732</v>
+        <v>-0.4413</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3732</v>
+        <v>-0.4413</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3732</v>
+        <v>-0.4413</v>
       </c>
       <c r="N24" t="n">
         <v>125</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5094</v>
+        <v>-0.4925</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1704</v>
+        <v>-0.1648</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8561</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5094</v>
+        <v>-0.4925</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5094</v>
+        <v>-0.4925</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5094</v>
+        <v>-0.4925</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5094</v>
+        <v>-0.4925</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5094</v>
+        <v>-0.4925</v>
       </c>
       <c r="N25" t="n">
         <v>128</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.602</v>
+        <v>-0.4987</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2014</v>
+        <v>-0.1669</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8982</v>
+        <v>-0.833</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.602</v>
+        <v>-0.4987</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9466</v>
+        <v>-0.9001</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3446</v>
+        <v>0.4014</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9466</v>
+        <v>-0.9001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.996</v>
+        <v>-0.9488</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3446</v>
+        <v>0.4014</v>
       </c>
       <c r="K26" t="n">
         <v>142</v>
@@ -1633,7 +1633,7 @@
         <v>71</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6514</v>
+        <v>-0.5474</v>
       </c>
       <c r="N26" t="n">
         <v>213</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6599</v>
+        <v>-0.652</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2208</v>
+        <v>-0.2181</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9246</v>
+        <v>-0.9028</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6599</v>
+        <v>-0.652</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6599</v>
+        <v>-0.652</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.6599</v>
+        <v>-0.652</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6599</v>
+        <v>-0.652</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.6599</v>
+        <v>-0.652</v>
       </c>
       <c r="N27" t="n">
         <v>125</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.8385</v>
+        <v>-0.8259</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2805</v>
+        <v>-0.2763</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0059</v>
+        <v>-0.982</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.8385</v>
+        <v>-0.8259</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.8385</v>
+        <v>-0.8259</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.8385</v>
+        <v>-0.8259</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8385</v>
+        <v>-0.8259</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.8385</v>
+        <v>-0.8259</v>
       </c>
       <c r="N28" t="n">
         <v>125</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.4906</v>
+        <v>-1.4194</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.4987</v>
+        <v>-0.4749</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.3028</v>
+        <v>-1.2524</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.4906</v>
+        <v>-1.4194</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.4906</v>
+        <v>-1.4194</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.4906</v>
+        <v>-1.4194</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.4906</v>
+        <v>-1.4194</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.4906</v>
+        <v>-1.4194</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.7744</v>
+        <v>-1.6815</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.5937</v>
+        <v>-0.5626</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.4319</v>
+        <v>-1.3718</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.7744</v>
+        <v>-1.6815</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.7744</v>
+        <v>-1.6815</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.7744</v>
+        <v>-1.6815</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.7744</v>
+        <v>-1.6815</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.7744</v>
+        <v>-1.6815</v>
       </c>
       <c r="N30" t="n">
         <v>128</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.0618</v>
+        <v>-1.9843</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6898</v>
+        <v>-0.6639</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.5628</v>
+        <v>-1.5097</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.0618</v>
+        <v>-1.9843</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.0618</v>
+        <v>-1.9843</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.0618</v>
+        <v>-1.9843</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.0618</v>
+        <v>-1.9843</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.0618</v>
+        <v>-1.9843</v>
       </c>
       <c r="N31" t="n">
         <v>128</v>
@@ -1969,10 +1969,10 @@
         <v>1.24</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3989</v>
+        <v>0.3963</v>
       </c>
       <c r="J2" t="n">
-        <v>11.5681</v>
+        <v>11.4927</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>0.187</v>
+        <v>0.1698</v>
       </c>
       <c r="J3" t="n">
-        <v>5.423</v>
+        <v>4.9242</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0411</v>
+        <v>-0.0317</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.1919</v>
+        <v>-0.9193</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1665</v>
+        <v>-0.1465</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.8285</v>
+        <v>-4.2485</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.65</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3902</v>
+        <v>-0.3787</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.3158</v>
+        <v>-10.9823</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.21</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3205</v>
+        <v>0.2635</v>
       </c>
       <c r="J7" t="n">
-        <v>9.294499999999999</v>
+        <v>7.6415</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2834</v>
+        <v>0.2301</v>
       </c>
       <c r="J8" t="n">
-        <v>8.2186</v>
+        <v>6.6729</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2188</v>
+        <v>0.1734</v>
       </c>
       <c r="J9" t="n">
-        <v>6.3452</v>
+        <v>5.0286</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1496</v>
+        <v>0.1148</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3384</v>
+        <v>3.3292</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1776</v>
+        <v>-0.1571</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.1504</v>
+        <v>-4.5559</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2285</v>
+        <v>1.2482</v>
       </c>
       <c r="J12" t="n">
-        <v>29.484</v>
+        <v>29.9568</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.368</v>
+        <v>0.3322</v>
       </c>
       <c r="J13" t="n">
-        <v>8.832000000000001</v>
+        <v>7.9728</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.368</v>
+        <v>0.3322</v>
       </c>
       <c r="J14" t="n">
-        <v>8.832000000000001</v>
+        <v>7.9728</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.03</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1122</v>
+        <v>0.0912</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6928</v>
+        <v>2.1888</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.96</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1971</v>
+        <v>-0.1624</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.7304</v>
+        <v>-3.8976</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2088</v>
+        <v>0.1665</v>
       </c>
       <c r="J17" t="n">
-        <v>5.0112</v>
+        <v>3.996</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>0.95</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0805</v>
+        <v>-0.0672</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.932</v>
+        <v>-1.6128</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0934</v>
+        <v>-0.0789</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.2416</v>
+        <v>-1.8936</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1176</v>
+        <v>-0.1011</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.8224</v>
+        <v>-2.4264</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3488</v>
+        <v>-0.3336</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.3712</v>
+        <v>-8.006399999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.99</v>
       </c>
       <c r="I22" t="n">
-        <v>1.788</v>
+        <v>1.8272</v>
       </c>
       <c r="J22" t="n">
-        <v>32.184</v>
+        <v>32.8896</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.74</v>
       </c>
       <c r="I23" t="n">
-        <v>1.474</v>
+        <v>1.5109</v>
       </c>
       <c r="J23" t="n">
-        <v>26.532</v>
+        <v>27.1962</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.64</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3134</v>
+        <v>1.3498</v>
       </c>
       <c r="J24" t="n">
-        <v>23.6412</v>
+        <v>24.2964</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.58</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2138</v>
+        <v>1.2401</v>
       </c>
       <c r="J25" t="n">
-        <v>21.8484</v>
+        <v>22.3218</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.78</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7174</v>
+        <v>-0.7003</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.9132</v>
+        <v>-12.6054</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.76</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2493</v>
+        <v>-0.2355</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.4874</v>
+        <v>-4.239</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.7</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3085</v>
+        <v>-0.2971</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.553</v>
+        <v>-5.3478</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.63</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3715</v>
+        <v>-0.3617</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.687</v>
+        <v>-6.5106</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.61</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3881</v>
+        <v>-0.3787</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.9858</v>
+        <v>-6.8166</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.44</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.537</v>
+        <v>-0.5395</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.666</v>
+        <v>-9.711</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2323</v>
+        <v>0.1878</v>
       </c>
       <c r="J32" t="n">
-        <v>6.969</v>
+        <v>5.634</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1698</v>
+        <v>0.1327</v>
       </c>
       <c r="J33" t="n">
-        <v>5.094</v>
+        <v>3.981</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0001</v>
+        <v>-0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.003</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.96</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0727</v>
+        <v>-0.0583</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.181</v>
+        <v>-1.749</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.9</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1471</v>
+        <v>-0.1275</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.413</v>
+        <v>-3.825</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.28</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5367</v>
+        <v>0.4777</v>
       </c>
       <c r="J37" t="n">
-        <v>16.101</v>
+        <v>14.331</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4097</v>
+        <v>0.3551</v>
       </c>
       <c r="J38" t="n">
-        <v>12.291</v>
+        <v>10.653</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.16</v>
       </c>
       <c r="I39" t="n">
-        <v>0.343</v>
+        <v>0.2926</v>
       </c>
       <c r="J39" t="n">
-        <v>10.29</v>
+        <v>8.778</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.06</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1561</v>
+        <v>0.1246</v>
       </c>
       <c r="J40" t="n">
-        <v>4.683</v>
+        <v>3.738</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.95</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0965</v>
+        <v>-0.0796</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.895</v>
+        <v>-2.388</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8524</v>
+        <v>0.8316</v>
       </c>
       <c r="J42" t="n">
-        <v>24.7196</v>
+        <v>24.1164</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.31</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.7468</v>
       </c>
       <c r="J43" t="n">
-        <v>22.4083</v>
+        <v>21.6572</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.25</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6501</v>
+        <v>0.6185</v>
       </c>
       <c r="J44" t="n">
-        <v>18.8529</v>
+        <v>17.9365</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.07</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2283</v>
+        <v>0.1987</v>
       </c>
       <c r="J45" t="n">
-        <v>6.6207</v>
+        <v>5.7623</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1038</v>
+        <v>0.0833</v>
       </c>
       <c r="J46" t="n">
-        <v>3.0102</v>
+        <v>2.4157</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.2</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4547</v>
+        <v>0.3982</v>
       </c>
       <c r="J47" t="n">
-        <v>13.1863</v>
+        <v>11.5478</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1383</v>
+        <v>0.1049</v>
       </c>
       <c r="J48" t="n">
-        <v>4.0107</v>
+        <v>3.0421</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2048</v>
+        <v>-0.1847</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.9392</v>
+        <v>-5.3563</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.78</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2647</v>
+        <v>-0.2453</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.6763</v>
+        <v>-7.1137</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.75</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2936</v>
+        <v>-0.2752</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.5144</v>
+        <v>-7.9808</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.2</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4319</v>
+        <v>0.3744</v>
       </c>
       <c r="J52" t="n">
-        <v>12.5251</v>
+        <v>10.8576</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2511</v>
+        <v>0.2048</v>
       </c>
       <c r="J53" t="n">
-        <v>7.2819</v>
+        <v>5.9392</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2111</v>
+        <v>0.169</v>
       </c>
       <c r="J54" t="n">
-        <v>6.1219</v>
+        <v>4.901</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.91</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1361</v>
+        <v>-0.1169</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.9469</v>
+        <v>-3.3901</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3017</v>
+        <v>-0.2839</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.7493</v>
+        <v>-8.2331</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.33</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8262</v>
+        <v>0.8021</v>
       </c>
       <c r="J57" t="n">
-        <v>23.9598</v>
+        <v>23.2609</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.18</v>
       </c>
       <c r="I58" t="n">
-        <v>0.508</v>
+        <v>0.4704</v>
       </c>
       <c r="J58" t="n">
-        <v>14.732</v>
+        <v>13.6416</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.15</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4399</v>
+        <v>0.4025</v>
       </c>
       <c r="J59" t="n">
-        <v>12.7571</v>
+        <v>11.6725</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1475</v>
+        <v>0.1229</v>
       </c>
       <c r="J60" t="n">
-        <v>4.2775</v>
+        <v>3.5641</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>1.02</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0775</v>
+        <v>0.0608</v>
       </c>
       <c r="J61" t="n">
-        <v>2.2475</v>
+        <v>1.7632</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.88</v>
       </c>
       <c r="I62" t="n">
-        <v>1.6033</v>
+        <v>1.6503</v>
       </c>
       <c r="J62" t="n">
-        <v>44.8924</v>
+        <v>46.2084</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7134</v>
+        <v>0.6839</v>
       </c>
       <c r="J63" t="n">
-        <v>19.9752</v>
+        <v>19.1492</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.03</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1052</v>
+        <v>0.0847</v>
       </c>
       <c r="J64" t="n">
-        <v>2.9456</v>
+        <v>2.3716</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.95</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2362</v>
+        <v>-0.1996</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.6136</v>
+        <v>-5.5888</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.83</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5543</v>
+        <v>-0.5167</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.5204</v>
+        <v>-14.4676</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.28</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6078</v>
+        <v>0.5556</v>
       </c>
       <c r="J67" t="n">
-        <v>17.0184</v>
+        <v>15.5568</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.06</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1969</v>
+        <v>0.1568</v>
       </c>
       <c r="J68" t="n">
-        <v>5.5132</v>
+        <v>4.3904</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.83</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2106</v>
+        <v>-0.1914</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.8968</v>
+        <v>-5.3592</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.63</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3991</v>
+        <v>-0.3877</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.1748</v>
+        <v>-10.8556</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.57</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4522</v>
+        <v>-0.4462</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.6616</v>
+        <v>-12.4936</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.58</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1981</v>
+        <v>1.2129</v>
       </c>
       <c r="J72" t="n">
-        <v>29.9525</v>
+        <v>30.3225</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8011</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>20.0275</v>
+        <v>19.4925</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.23</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6018</v>
+        <v>0.5722</v>
       </c>
       <c r="J74" t="n">
-        <v>15.045</v>
+        <v>14.305</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.12</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3506</v>
+        <v>0.3182</v>
       </c>
       <c r="J75" t="n">
-        <v>8.765000000000001</v>
+        <v>7.955</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.07</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2176</v>
+        <v>0.1885</v>
       </c>
       <c r="J76" t="n">
-        <v>5.44</v>
+        <v>4.7125</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="I77" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>2.3325</v>
+        <v>1.8725</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.89</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.138</v>
+        <v>-0.1227</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.45</v>
+        <v>-3.0675</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2132</v>
+        <v>-0.1967</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.33</v>
+        <v>-4.9175</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.62</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3978</v>
+        <v>-0.3861</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.945</v>
+        <v>-9.6525</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.451</v>
+        <v>-0.4442</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.275</v>
+        <v>-11.105</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>0.7</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.2853</v>
+        <v>-0.2724</v>
       </c>
       <c r="J82" t="n">
-        <v>-5.1354</v>
+        <v>-4.9032</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>0.55</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.4283</v>
+        <v>-0.4246</v>
       </c>
       <c r="J83" t="n">
-        <v>-7.7094</v>
+        <v>-7.6428</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.54</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.4367</v>
+        <v>-0.4332</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.8606</v>
+        <v>-7.7976</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.44</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.522</v>
+        <v>-0.5231</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.396000000000001</v>
+        <v>-9.415800000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.43</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5309</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.5562</v>
+        <v>-9.590400000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.74</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3474</v>
+        <v>1.3732</v>
       </c>
       <c r="J87" t="n">
-        <v>24.2532</v>
+        <v>24.7176</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.65</v>
       </c>
       <c r="I88" t="n">
-        <v>1.2399</v>
+        <v>1.2628</v>
       </c>
       <c r="J88" t="n">
-        <v>22.3182</v>
+        <v>22.7304</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.61</v>
       </c>
       <c r="I89" t="n">
-        <v>1.192</v>
+        <v>1.2142</v>
       </c>
       <c r="J89" t="n">
-        <v>21.456</v>
+        <v>21.8556</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>1.58</v>
       </c>
       <c r="I90" t="n">
-        <v>1.1561</v>
+        <v>1.1777</v>
       </c>
       <c r="J90" t="n">
-        <v>20.8098</v>
+        <v>21.1986</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>1.44</v>
       </c>
       <c r="I91" t="n">
-        <v>0.964</v>
+        <v>0.9705</v>
       </c>
       <c r="J91" t="n">
-        <v>17.352</v>
+        <v>17.469</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.84</v>
       </c>
       <c r="I92" t="n">
-        <v>1.5278</v>
+        <v>1.5636</v>
       </c>
       <c r="J92" t="n">
-        <v>39.7228</v>
+        <v>40.6536</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.33</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7993</v>
+        <v>0.7784</v>
       </c>
       <c r="J93" t="n">
-        <v>20.7818</v>
+        <v>20.2384</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.22</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5494</v>
       </c>
       <c r="J94" t="n">
-        <v>15.0566</v>
+        <v>14.2844</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1866</v>
+        <v>0.1588</v>
       </c>
       <c r="J95" t="n">
-        <v>4.8516</v>
+        <v>4.1288</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.281</v>
+        <v>-0.2443</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.306</v>
+        <v>-6.3518</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2581</v>
+        <v>0.2149</v>
       </c>
       <c r="J97" t="n">
-        <v>6.7106</v>
+        <v>5.5874</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>0.86</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1762</v>
+        <v>-0.1594</v>
       </c>
       <c r="J98" t="n">
-        <v>-4.5812</v>
+        <v>-4.1444</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>0.78</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2547</v>
+        <v>-0.2366</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.6222</v>
+        <v>-6.1516</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.72</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3113</v>
+        <v>-0.2943</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.0938</v>
+        <v>-7.6518</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.66</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3663</v>
+        <v>-0.3522</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.5238</v>
+        <v>-9.1572</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.54</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1462</v>
+        <v>1.1592</v>
       </c>
       <c r="J102" t="n">
-        <v>27.5088</v>
+        <v>27.8208</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7431</v>
+        <v>0.7183</v>
       </c>
       <c r="J103" t="n">
-        <v>17.8344</v>
+        <v>17.2392</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.23</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6025</v>
+        <v>0.5727</v>
       </c>
       <c r="J104" t="n">
-        <v>14.46</v>
+        <v>13.7448</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.14</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4007</v>
+        <v>0.368</v>
       </c>
       <c r="J105" t="n">
-        <v>9.6168</v>
+        <v>8.832000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>1.09</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2739</v>
+        <v>0.2428</v>
       </c>
       <c r="J106" t="n">
-        <v>6.5736</v>
+        <v>5.8272</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.03</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1415</v>
+        <v>0.1114</v>
       </c>
       <c r="J107" t="n">
-        <v>3.396</v>
+        <v>2.6736</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>0.88</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1539</v>
+        <v>-0.1378</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.6936</v>
+        <v>-3.3072</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2064</v>
+        <v>-0.189</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.9536</v>
+        <v>-4.536</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.7</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3291</v>
+        <v>-0.3129</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.8984</v>
+        <v>-7.5096</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.63</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3927</v>
+        <v>-0.3806</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.424799999999999</v>
+        <v>-9.134399999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1216</v>
+        <v>1.1339</v>
       </c>
       <c r="J112" t="n">
-        <v>25.7968</v>
+        <v>26.0797</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.4</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9384</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>21.5832</v>
+        <v>21.3187</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8625</v>
+        <v>0.8442</v>
       </c>
       <c r="J114" t="n">
-        <v>19.8375</v>
+        <v>19.4166</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3783</v>
+        <v>0.3454</v>
       </c>
       <c r="J115" t="n">
-        <v>8.700900000000001</v>
+        <v>7.9442</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.83</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5633</v>
+        <v>-0.5275</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.9559</v>
+        <v>-12.1325</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.24</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5294</v>
+        <v>0.4734</v>
       </c>
       <c r="J117" t="n">
-        <v>12.1762</v>
+        <v>10.8882</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.05</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1662</v>
+        <v>0.1291</v>
       </c>
       <c r="J118" t="n">
-        <v>3.8226</v>
+        <v>2.9693</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.92</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.117</v>
+        <v>-0.1008</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.691</v>
+        <v>-2.3184</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.76</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2822</v>
+        <v>-0.2634</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.4906</v>
+        <v>-6.0582</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4724</v>
+        <v>-0.4692</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.8652</v>
+        <v>-10.7916</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1235</v>
+        <v>1.1367</v>
       </c>
       <c r="J122" t="n">
-        <v>33.705</v>
+        <v>34.101</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.32</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8121</v>
+        <v>0.7866</v>
       </c>
       <c r="J123" t="n">
-        <v>24.363</v>
+        <v>23.598</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.23</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6227</v>
+        <v>0.5866</v>
       </c>
       <c r="J124" t="n">
-        <v>18.681</v>
+        <v>17.598</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3386</v>
+        <v>-0.2966</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.158</v>
+        <v>-8.898</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.64</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.957</v>
+        <v>-0.9512</v>
       </c>
       <c r="J126" t="n">
-        <v>-28.71</v>
+        <v>-28.536</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2979</v>
+        <v>0.2474</v>
       </c>
       <c r="J127" t="n">
-        <v>8.936999999999999</v>
+        <v>7.422</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0035</v>
+        <v>0.0018</v>
       </c>
       <c r="J128" t="n">
-        <v>0.105</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.99</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0235</v>
+        <v>-0.0173</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.705</v>
+        <v>-0.519</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.91</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1326</v>
+        <v>-0.114</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.978</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2393</v>
+        <v>-0.2191</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.179</v>
+        <v>-6.573</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.76</v>
       </c>
       <c r="I132" t="n">
-        <v>1.468</v>
+        <v>1.5042</v>
       </c>
       <c r="J132" t="n">
-        <v>39.636</v>
+        <v>40.6134</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.47</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0761</v>
+        <v>1.0854</v>
       </c>
       <c r="J133" t="n">
-        <v>29.0547</v>
+        <v>29.3058</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.97</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1607</v>
+        <v>-0.1292</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.3389</v>
+        <v>-3.4884</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6149</v>
+        <v>-0.579</v>
       </c>
       <c r="J135" t="n">
-        <v>-16.6023</v>
+        <v>-15.633</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.7</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.8166</v>
       </c>
       <c r="J136" t="n">
-        <v>-22.5504</v>
+        <v>-22.0482</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4779</v>
+        <v>0.4218</v>
       </c>
       <c r="J137" t="n">
-        <v>12.9033</v>
+        <v>11.3886</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0926</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.5002</v>
+        <v>-2.1141</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.9</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1395</v>
+        <v>-0.1219</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.7665</v>
+        <v>-3.2913</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.76</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2822</v>
+        <v>-0.2634</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.6194</v>
+        <v>-7.1118</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3294</v>
+        <v>-0.3128</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.893800000000001</v>
+        <v>-8.445600000000001</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.182</v>
+        <v>-0.1625</v>
       </c>
       <c r="J142" t="n">
-        <v>-3.458</v>
+        <v>-3.0875</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>0.64</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.3557</v>
+        <v>-0.3475</v>
       </c>
       <c r="J143" t="n">
-        <v>-6.7583</v>
+        <v>-6.6025</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.6</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3917</v>
+        <v>-0.3847</v>
       </c>
       <c r="J144" t="n">
-        <v>-7.4423</v>
+        <v>-7.3093</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.44</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5296</v>
+        <v>-0.531</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.0624</v>
+        <v>-10.089</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.4</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5709</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.735</v>
+        <v>-10.8471</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>2.71</v>
       </c>
       <c r="I147" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J147" t="n">
-        <v>36.8068</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.8</v>
       </c>
       <c r="I148" t="n">
-        <v>1.4264</v>
+        <v>1.4543</v>
       </c>
       <c r="J148" t="n">
-        <v>27.1016</v>
+        <v>27.6317</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.45</v>
       </c>
       <c r="I149" t="n">
-        <v>0.9872</v>
+        <v>0.9951</v>
       </c>
       <c r="J149" t="n">
-        <v>18.7568</v>
+        <v>18.9069</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>1.05</v>
       </c>
       <c r="I150" t="n">
-        <v>0.117</v>
+        <v>0.0861</v>
       </c>
       <c r="J150" t="n">
-        <v>2.223</v>
+        <v>1.6359</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.7</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8878</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.8682</v>
+        <v>-16.8454</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9387</v>
+        <v>0.929</v>
       </c>
       <c r="J152" t="n">
-        <v>27.2223</v>
+        <v>26.941</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5907</v>
+        <v>0.5515</v>
       </c>
       <c r="J153" t="n">
-        <v>17.1303</v>
+        <v>15.9935</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2576</v>
+        <v>-0.2195</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.4704</v>
+        <v>-6.3655</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3132</v>
+        <v>-0.2724</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.082800000000001</v>
+        <v>-7.8996</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.1163</v>
+        <v>-1.1278</v>
       </c>
       <c r="J156" t="n">
-        <v>-32.3727</v>
+        <v>-32.7062</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.33</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6168</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>17.8872</v>
+        <v>16.153</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.23</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4614</v>
+        <v>0.404</v>
       </c>
       <c r="J158" t="n">
-        <v>13.3806</v>
+        <v>11.716</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1585</v>
+        <v>0.1263</v>
       </c>
       <c r="J159" t="n">
-        <v>4.5965</v>
+        <v>3.6627</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.01</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0312</v>
+        <v>0.0215</v>
       </c>
       <c r="J160" t="n">
-        <v>0.9048</v>
+        <v>0.6235000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.92</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1328</v>
+        <v>-0.1136</v>
       </c>
       <c r="J161" t="n">
-        <v>-3.8512</v>
+        <v>-3.2944</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.2</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4744</v>
+        <v>0.4206</v>
       </c>
       <c r="J162" t="n">
-        <v>11.86</v>
+        <v>10.515</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>0.8</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2395</v>
+        <v>-0.2203</v>
       </c>
       <c r="J163" t="n">
-        <v>-5.9875</v>
+        <v>-5.5075</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>0.8</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2395</v>
+        <v>-0.2203</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.9875</v>
+        <v>-5.5075</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.78</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.259</v>
+        <v>-0.24</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.475</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2972</v>
+        <v>-0.2792</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.43</v>
+        <v>-6.98</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8398</v>
+        <v>0.8173</v>
       </c>
       <c r="J167" t="n">
-        <v>20.995</v>
+        <v>20.4325</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.23</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6131</v>
+        <v>0.5788</v>
       </c>
       <c r="J168" t="n">
-        <v>15.3275</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.17</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4827</v>
+        <v>0.4465</v>
       </c>
       <c r="J169" t="n">
-        <v>12.0675</v>
+        <v>11.1625</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>1.14</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4141</v>
+        <v>0.3783</v>
       </c>
       <c r="J170" t="n">
-        <v>10.3525</v>
+        <v>9.4575</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1662</v>
+        <v>-0.1346</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.155</v>
+        <v>-3.365</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>0.91</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1147</v>
+        <v>-0.1001</v>
       </c>
       <c r="J172" t="n">
-        <v>-2.6381</v>
+        <v>-2.3023</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>0.83</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2033</v>
+        <v>-0.1869</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.6759</v>
+        <v>-4.2987</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>0.79</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2426</v>
+        <v>-0.2257</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.5798</v>
+        <v>-5.1911</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.78</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2517</v>
+        <v>-0.2348</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.7891</v>
+        <v>-5.4004</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4159</v>
+        <v>-0.4057</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.5657</v>
+        <v>-9.331099999999999</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.63</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2616</v>
+        <v>1.279</v>
       </c>
       <c r="J177" t="n">
-        <v>29.0168</v>
+        <v>29.417</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.31</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7376</v>
       </c>
       <c r="J178" t="n">
-        <v>17.4938</v>
+        <v>16.9648</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.16</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4456</v>
+        <v>0.4134</v>
       </c>
       <c r="J179" t="n">
-        <v>10.2488</v>
+        <v>9.5082</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.16</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4456</v>
+        <v>0.4134</v>
       </c>
       <c r="J180" t="n">
-        <v>10.2488</v>
+        <v>9.5082</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.12</v>
       </c>
       <c r="I181" t="n">
-        <v>0.349</v>
+        <v>0.3168</v>
       </c>
       <c r="J181" t="n">
-        <v>8.026999999999999</v>
+        <v>7.2864</v>
       </c>
     </row>
   </sheetData>
